--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_DEER_BUCK_DRAW.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_DEER_BUCK_DRAW.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N462"/>
+  <dimension ref="A1:O462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -598,10 +599,15 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -653,7 +659,8 @@
       </c>
       <c r="L4" s="4" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -701,7 +708,8 @@
       </c>
       <c r="L5" s="6" t="inlineStr"/>
       <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -749,7 +757,8 @@
       </c>
       <c r="L6" s="4" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -797,7 +806,8 @@
       </c>
       <c r="L7" s="6" t="inlineStr"/>
       <c r="M7" s="6" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -845,7 +855,8 @@
       </c>
       <c r="L8" s="4" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -893,7 +904,8 @@
       </c>
       <c r="L9" s="6" t="inlineStr"/>
       <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -945,7 +957,8 @@
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -1001,7 +1014,8 @@
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1053,7 +1067,8 @@
       </c>
       <c r="L12" s="4" t="inlineStr"/>
       <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1101,7 +1116,8 @@
       </c>
       <c r="L13" s="6" t="inlineStr"/>
       <c r="M13" s="6" t="inlineStr"/>
-      <c r="N13" s="6" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -1149,7 +1165,8 @@
       </c>
       <c r="L14" s="4" t="inlineStr"/>
       <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1197,7 +1214,8 @@
       </c>
       <c r="L15" s="6" t="inlineStr"/>
       <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="6" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -1260,8 +1278,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
@@ -1328,8 +1351,13 @@
           <t>67.6</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="6" t="inlineStr">
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
@@ -1397,7 +1425,8 @@
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1464,8 +1493,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="6" t="inlineStr">
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -1532,8 +1566,13 @@
           <t>93.2</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
@@ -1600,8 +1639,13 @@
           <t>90</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr"/>
-      <c r="N21" s="6" t="inlineStr">
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
@@ -1668,8 +1712,13 @@
           <t>70</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -1736,8 +1785,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="6" t="inlineStr">
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1804,8 +1858,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
@@ -1873,7 +1932,8 @@
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr"/>
-      <c r="N25" s="6" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
@@ -1940,8 +2000,13 @@
           <t>92.9</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
@@ -2009,7 +2074,8 @@
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr"/>
-      <c r="N27" s="6" t="inlineStr">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" s="6" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
@@ -2077,7 +2143,8 @@
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>9.2</t>
         </is>
@@ -2145,7 +2212,8 @@
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr"/>
-      <c r="N29" s="6" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" s="6" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
@@ -2213,7 +2281,8 @@
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr"/>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -2281,7 +2350,8 @@
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr"/>
-      <c r="N31" s="6" t="inlineStr">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" s="6" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
@@ -2349,7 +2419,8 @@
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr"/>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>8.8</t>
         </is>
@@ -2417,7 +2488,8 @@
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr"/>
-      <c r="N33" s="6" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" s="6" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -2485,7 +2557,8 @@
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr"/>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -2553,7 +2626,8 @@
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr"/>
-      <c r="N35" s="6" t="inlineStr">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" s="6" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -2621,7 +2695,8 @@
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr"/>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2689,7 +2764,8 @@
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr"/>
-      <c r="N37" s="6" t="inlineStr">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" s="6" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -2757,7 +2833,8 @@
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr"/>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -2825,7 +2902,8 @@
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr"/>
-      <c r="N39" s="6" t="inlineStr">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" s="6" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -2893,7 +2971,8 @@
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr"/>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -2961,7 +3040,8 @@
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr"/>
-      <c r="N41" s="6" t="inlineStr">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" s="6" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -3029,7 +3109,8 @@
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr"/>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
@@ -3097,7 +3178,8 @@
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr"/>
-      <c r="N43" s="6" t="inlineStr">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -3165,7 +3247,8 @@
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr"/>
-      <c r="N44" s="4" t="inlineStr">
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -3233,7 +3316,8 @@
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr"/>
-      <c r="N45" s="6" t="inlineStr">
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" s="6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -3301,7 +3385,8 @@
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr"/>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -3369,7 +3454,8 @@
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr"/>
-      <c r="N47" s="6" t="inlineStr">
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" s="6" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -3437,7 +3523,8 @@
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr"/>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
@@ -3505,7 +3592,8 @@
         </is>
       </c>
       <c r="M49" s="6" t="inlineStr"/>
-      <c r="N49" s="6" t="inlineStr">
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" s="6" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -3573,7 +3661,8 @@
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr"/>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -3641,7 +3730,8 @@
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr"/>
-      <c r="N51" s="6" t="inlineStr">
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" s="6" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -3709,7 +3799,8 @@
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr"/>
-      <c r="N52" s="4" t="inlineStr">
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
@@ -3777,7 +3868,8 @@
         </is>
       </c>
       <c r="M53" s="6" t="inlineStr"/>
-      <c r="N53" s="6" t="inlineStr">
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" s="6" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -3845,7 +3937,8 @@
         </is>
       </c>
       <c r="M54" s="4" t="inlineStr"/>
-      <c r="N54" s="4" t="inlineStr">
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -3913,7 +4006,8 @@
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr"/>
-      <c r="N55" s="6" t="inlineStr">
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" s="6" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
@@ -3981,7 +4075,8 @@
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr"/>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" s="4" t="inlineStr">
         <is>
           <t>15.3</t>
         </is>
@@ -4049,7 +4144,8 @@
         </is>
       </c>
       <c r="M57" s="6" t="inlineStr"/>
-      <c r="N57" s="6" t="inlineStr">
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" s="6" t="inlineStr">
         <is>
           <t>30.3</t>
         </is>
@@ -4117,7 +4213,8 @@
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr"/>
-      <c r="N58" s="4" t="inlineStr">
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -4185,7 +4282,8 @@
         </is>
       </c>
       <c r="M59" s="6" t="inlineStr"/>
-      <c r="N59" s="6" t="inlineStr">
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" s="6" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
@@ -4253,7 +4351,8 @@
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr"/>
-      <c r="N60" s="4" t="inlineStr">
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -4321,7 +4420,8 @@
         </is>
       </c>
       <c r="M61" s="6" t="inlineStr"/>
-      <c r="N61" s="6" t="inlineStr">
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" s="6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -4389,7 +4489,8 @@
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr"/>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" s="4" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
@@ -4457,7 +4558,8 @@
         </is>
       </c>
       <c r="M63" s="6" t="inlineStr"/>
-      <c r="N63" s="6" t="inlineStr">
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -4513,7 +4615,8 @@
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr"/>
-      <c r="N64" s="4" t="inlineStr">
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -4580,8 +4683,13 @@
           <t>37</t>
         </is>
       </c>
-      <c r="M65" s="6" t="inlineStr"/>
-      <c r="N65" s="6" t="inlineStr">
+      <c r="M65" s="6" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" s="6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
@@ -4649,7 +4757,8 @@
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr"/>
-      <c r="N66" s="4" t="inlineStr">
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" s="4" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -4716,8 +4825,13 @@
           <t>88.9</t>
         </is>
       </c>
-      <c r="M67" s="6" t="inlineStr"/>
-      <c r="N67" s="6" t="inlineStr">
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" s="6" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
@@ -4784,8 +4898,13 @@
           <t>55.6</t>
         </is>
       </c>
-      <c r="M68" s="4" t="inlineStr"/>
-      <c r="N68" s="4" t="inlineStr">
+      <c r="M68" s="4" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" s="4" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
@@ -4837,7 +4956,8 @@
       </c>
       <c r="L69" s="6" t="inlineStr"/>
       <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="6" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" s="6" t="inlineStr"/>
     </row>
     <row r="70" ht="24" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
@@ -4885,7 +5005,8 @@
       </c>
       <c r="L70" s="4" t="inlineStr"/>
       <c r="M70" s="4" t="inlineStr"/>
-      <c r="N70" s="4" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" s="4" t="inlineStr"/>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
@@ -4949,7 +5070,8 @@
         </is>
       </c>
       <c r="M71" s="6" t="inlineStr"/>
-      <c r="N71" s="6" t="inlineStr">
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" s="6" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -5017,7 +5139,8 @@
         </is>
       </c>
       <c r="M72" s="4" t="inlineStr"/>
-      <c r="N72" s="4" t="inlineStr">
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" s="4" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -5085,7 +5208,8 @@
         </is>
       </c>
       <c r="M73" s="6" t="inlineStr"/>
-      <c r="N73" s="6" t="inlineStr">
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" s="6" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -5153,7 +5277,8 @@
         </is>
       </c>
       <c r="M74" s="4" t="inlineStr"/>
-      <c r="N74" s="4" t="inlineStr">
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" s="4" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -5221,7 +5346,8 @@
         </is>
       </c>
       <c r="M75" s="6" t="inlineStr"/>
-      <c r="N75" s="6" t="inlineStr">
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" s="6" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -5289,7 +5415,8 @@
         </is>
       </c>
       <c r="M76" s="4" t="inlineStr"/>
-      <c r="N76" s="4" t="inlineStr">
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" s="4" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
@@ -5357,7 +5484,8 @@
         </is>
       </c>
       <c r="M77" s="6" t="inlineStr"/>
-      <c r="N77" s="6" t="inlineStr">
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -5425,7 +5553,8 @@
         </is>
       </c>
       <c r="M78" s="4" t="inlineStr"/>
-      <c r="N78" s="4" t="inlineStr">
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" s="4" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
@@ -5493,7 +5622,8 @@
         </is>
       </c>
       <c r="M79" s="6" t="inlineStr"/>
-      <c r="N79" s="6" t="inlineStr">
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -5561,7 +5691,8 @@
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr"/>
-      <c r="N80" s="4" t="inlineStr">
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -5629,7 +5760,8 @@
         </is>
       </c>
       <c r="M81" s="6" t="inlineStr"/>
-      <c r="N81" s="6" t="inlineStr">
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -5697,7 +5829,8 @@
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr"/>
-      <c r="N82" s="4" t="inlineStr">
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -5765,7 +5898,8 @@
         </is>
       </c>
       <c r="M83" s="6" t="inlineStr"/>
-      <c r="N83" s="6" t="inlineStr">
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -5833,7 +5967,8 @@
         </is>
       </c>
       <c r="M84" s="4" t="inlineStr"/>
-      <c r="N84" s="4" t="inlineStr">
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" s="4" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -5901,7 +6036,8 @@
         </is>
       </c>
       <c r="M85" s="6" t="inlineStr"/>
-      <c r="N85" s="6" t="inlineStr">
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -5969,7 +6105,8 @@
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr"/>
-      <c r="N86" s="4" t="inlineStr">
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -6037,7 +6174,8 @@
         </is>
       </c>
       <c r="M87" s="6" t="inlineStr"/>
-      <c r="N87" s="6" t="inlineStr">
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" s="6" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -6105,7 +6243,8 @@
         </is>
       </c>
       <c r="M88" s="4" t="inlineStr"/>
-      <c r="N88" s="4" t="inlineStr">
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -6173,7 +6312,8 @@
         </is>
       </c>
       <c r="M89" s="6" t="inlineStr"/>
-      <c r="N89" s="6" t="inlineStr">
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -6241,7 +6381,8 @@
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr"/>
-      <c r="N90" s="4" t="inlineStr">
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" s="4" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -6309,7 +6450,8 @@
         </is>
       </c>
       <c r="M91" s="6" t="inlineStr"/>
-      <c r="N91" s="6" t="inlineStr">
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" s="6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
@@ -6377,7 +6519,8 @@
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr"/>
-      <c r="N92" s="4" t="inlineStr">
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" s="4" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
@@ -6445,7 +6588,8 @@
         </is>
       </c>
       <c r="M93" s="6" t="inlineStr"/>
-      <c r="N93" s="6" t="inlineStr">
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -6513,7 +6657,8 @@
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr"/>
-      <c r="N94" s="4" t="inlineStr">
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" s="4" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -6581,7 +6726,8 @@
         </is>
       </c>
       <c r="M95" s="6" t="inlineStr"/>
-      <c r="N95" s="6" t="inlineStr">
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" s="6" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -6649,7 +6795,8 @@
         </is>
       </c>
       <c r="M96" s="4" t="inlineStr"/>
-      <c r="N96" s="4" t="inlineStr">
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" s="4" t="inlineStr">
         <is>
           <t>11.8</t>
         </is>
@@ -6717,7 +6864,8 @@
         </is>
       </c>
       <c r="M97" s="6" t="inlineStr"/>
-      <c r="N97" s="6" t="inlineStr">
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" s="6" t="inlineStr">
         <is>
           <t>13.8</t>
         </is>
@@ -6769,7 +6917,8 @@
       </c>
       <c r="L98" s="4" t="inlineStr"/>
       <c r="M98" s="4" t="inlineStr"/>
-      <c r="N98" s="4" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" s="4" t="inlineStr"/>
     </row>
     <row r="99" ht="24" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
@@ -6833,7 +6982,8 @@
         </is>
       </c>
       <c r="M99" s="6" t="inlineStr"/>
-      <c r="N99" s="6" t="inlineStr">
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -6901,7 +7051,8 @@
         </is>
       </c>
       <c r="M100" s="4" t="inlineStr"/>
-      <c r="N100" s="4" t="inlineStr">
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" s="4" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -6965,7 +7116,8 @@
       </c>
       <c r="L101" s="6" t="inlineStr"/>
       <c r="M101" s="6" t="inlineStr"/>
-      <c r="N101" s="6" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" s="6" t="inlineStr"/>
     </row>
     <row r="102" ht="24" customHeight="1">
       <c r="A102" s="3" t="inlineStr">
@@ -7029,7 +7181,8 @@
         </is>
       </c>
       <c r="M102" s="4" t="inlineStr"/>
-      <c r="N102" s="4" t="inlineStr">
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -7097,7 +7250,8 @@
         </is>
       </c>
       <c r="M103" s="6" t="inlineStr"/>
-      <c r="N103" s="6" t="inlineStr">
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" s="6" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
@@ -7165,7 +7319,8 @@
         </is>
       </c>
       <c r="M104" s="4" t="inlineStr"/>
-      <c r="N104" s="4" t="inlineStr">
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -7233,7 +7388,8 @@
         </is>
       </c>
       <c r="M105" s="6" t="inlineStr"/>
-      <c r="N105" s="6" t="inlineStr">
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -7301,7 +7457,8 @@
         </is>
       </c>
       <c r="M106" s="4" t="inlineStr"/>
-      <c r="N106" s="4" t="inlineStr">
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" s="4" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
@@ -7369,7 +7526,8 @@
         </is>
       </c>
       <c r="M107" s="6" t="inlineStr"/>
-      <c r="N107" s="6" t="inlineStr">
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -7437,7 +7595,8 @@
         </is>
       </c>
       <c r="M108" s="4" t="inlineStr"/>
-      <c r="N108" s="4" t="inlineStr">
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -7505,7 +7664,8 @@
         </is>
       </c>
       <c r="M109" s="6" t="inlineStr"/>
-      <c r="N109" s="6" t="inlineStr">
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -7573,7 +7733,8 @@
         </is>
       </c>
       <c r="M110" s="4" t="inlineStr"/>
-      <c r="N110" s="4" t="inlineStr">
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -7641,7 +7802,8 @@
         </is>
       </c>
       <c r="M111" s="6" t="inlineStr"/>
-      <c r="N111" s="6" t="inlineStr">
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -7709,7 +7871,8 @@
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr"/>
-      <c r="N112" s="4" t="inlineStr">
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" s="4" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -7777,7 +7940,8 @@
         </is>
       </c>
       <c r="M113" s="6" t="inlineStr"/>
-      <c r="N113" s="6" t="inlineStr">
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -7845,7 +8009,8 @@
         </is>
       </c>
       <c r="M114" s="4" t="inlineStr"/>
-      <c r="N114" s="4" t="inlineStr">
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -7913,7 +8078,8 @@
         </is>
       </c>
       <c r="M115" s="6" t="inlineStr"/>
-      <c r="N115" s="6" t="inlineStr">
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -7981,7 +8147,8 @@
         </is>
       </c>
       <c r="M116" s="4" t="inlineStr"/>
-      <c r="N116" s="4" t="inlineStr">
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" s="4" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
@@ -8049,7 +8216,8 @@
         </is>
       </c>
       <c r="M117" s="6" t="inlineStr"/>
-      <c r="N117" s="6" t="inlineStr">
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -8117,7 +8285,8 @@
         </is>
       </c>
       <c r="M118" s="4" t="inlineStr"/>
-      <c r="N118" s="4" t="inlineStr">
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" s="4" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -8185,7 +8354,8 @@
         </is>
       </c>
       <c r="M119" s="6" t="inlineStr"/>
-      <c r="N119" s="6" t="inlineStr">
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" s="6" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
@@ -8253,7 +8423,8 @@
         </is>
       </c>
       <c r="M120" s="4" t="inlineStr"/>
-      <c r="N120" s="4" t="inlineStr">
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" s="4" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -8321,7 +8492,8 @@
         </is>
       </c>
       <c r="M121" s="6" t="inlineStr"/>
-      <c r="N121" s="6" t="inlineStr">
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" s="6" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -8389,7 +8561,8 @@
         </is>
       </c>
       <c r="M122" s="4" t="inlineStr"/>
-      <c r="N122" s="4" t="inlineStr">
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" s="4" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -8457,7 +8630,8 @@
         </is>
       </c>
       <c r="M123" s="6" t="inlineStr"/>
-      <c r="N123" s="6" t="inlineStr">
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" s="6" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -8525,7 +8699,8 @@
         </is>
       </c>
       <c r="M124" s="4" t="inlineStr"/>
-      <c r="N124" s="4" t="inlineStr">
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -8593,7 +8768,8 @@
         </is>
       </c>
       <c r="M125" s="6" t="inlineStr"/>
-      <c r="N125" s="6" t="inlineStr">
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" s="6" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -8661,7 +8837,8 @@
         </is>
       </c>
       <c r="M126" s="4" t="inlineStr"/>
-      <c r="N126" s="4" t="inlineStr">
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" s="4" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -8729,7 +8906,8 @@
         </is>
       </c>
       <c r="M127" s="6" t="inlineStr"/>
-      <c r="N127" s="6" t="inlineStr">
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" s="6" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
@@ -8797,7 +8975,8 @@
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr"/>
-      <c r="N128" s="4" t="inlineStr">
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -8865,7 +9044,8 @@
         </is>
       </c>
       <c r="M129" s="6" t="inlineStr"/>
-      <c r="N129" s="6" t="inlineStr">
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -8933,7 +9113,8 @@
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr"/>
-      <c r="N130" s="4" t="inlineStr">
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -9001,7 +9182,8 @@
         </is>
       </c>
       <c r="M131" s="6" t="inlineStr"/>
-      <c r="N131" s="6" t="inlineStr">
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" s="6" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -9069,7 +9251,8 @@
         </is>
       </c>
       <c r="M132" s="4" t="inlineStr"/>
-      <c r="N132" s="4" t="inlineStr">
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -9137,7 +9320,8 @@
         </is>
       </c>
       <c r="M133" s="6" t="inlineStr"/>
-      <c r="N133" s="6" t="inlineStr">
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" s="6" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -9205,7 +9389,8 @@
         </is>
       </c>
       <c r="M134" s="4" t="inlineStr"/>
-      <c r="N134" s="4" t="inlineStr">
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" s="4" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -9273,7 +9458,8 @@
         </is>
       </c>
       <c r="M135" s="6" t="inlineStr"/>
-      <c r="N135" s="6" t="inlineStr">
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" s="6" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -9341,7 +9527,8 @@
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr"/>
-      <c r="N136" s="4" t="inlineStr">
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -9409,7 +9596,8 @@
         </is>
       </c>
       <c r="M137" s="6" t="inlineStr"/>
-      <c r="N137" s="6" t="inlineStr">
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" s="6" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -9477,7 +9665,8 @@
         </is>
       </c>
       <c r="M138" s="4" t="inlineStr"/>
-      <c r="N138" s="4" t="inlineStr">
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -9545,7 +9734,8 @@
         </is>
       </c>
       <c r="M139" s="6" t="inlineStr"/>
-      <c r="N139" s="6" t="inlineStr">
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -9613,7 +9803,8 @@
         </is>
       </c>
       <c r="M140" s="4" t="inlineStr"/>
-      <c r="N140" s="4" t="inlineStr">
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -9681,7 +9872,8 @@
         </is>
       </c>
       <c r="M141" s="6" t="inlineStr"/>
-      <c r="N141" s="6" t="inlineStr">
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -9749,7 +9941,8 @@
         </is>
       </c>
       <c r="M142" s="4" t="inlineStr"/>
-      <c r="N142" s="4" t="inlineStr">
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" s="4" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
@@ -9817,7 +10010,8 @@
         </is>
       </c>
       <c r="M143" s="6" t="inlineStr"/>
-      <c r="N143" s="6" t="inlineStr">
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -9885,7 +10079,8 @@
         </is>
       </c>
       <c r="M144" s="4" t="inlineStr"/>
-      <c r="N144" s="4" t="inlineStr">
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -9953,7 +10148,8 @@
         </is>
       </c>
       <c r="M145" s="6" t="inlineStr"/>
-      <c r="N145" s="6" t="inlineStr">
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" s="6" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
@@ -10021,7 +10217,8 @@
         </is>
       </c>
       <c r="M146" s="4" t="inlineStr"/>
-      <c r="N146" s="4" t="inlineStr">
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" s="4" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -10089,7 +10286,8 @@
         </is>
       </c>
       <c r="M147" s="6" t="inlineStr"/>
-      <c r="N147" s="6" t="inlineStr">
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -10157,7 +10355,8 @@
         </is>
       </c>
       <c r="M148" s="4" t="inlineStr"/>
-      <c r="N148" s="4" t="inlineStr">
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -10225,7 +10424,8 @@
         </is>
       </c>
       <c r="M149" s="6" t="inlineStr"/>
-      <c r="N149" s="6" t="inlineStr">
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -10293,7 +10493,8 @@
         </is>
       </c>
       <c r="M150" s="4" t="inlineStr"/>
-      <c r="N150" s="4" t="inlineStr">
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" s="4" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -10361,7 +10562,8 @@
         </is>
       </c>
       <c r="M151" s="6" t="inlineStr"/>
-      <c r="N151" s="6" t="inlineStr">
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" s="6" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
@@ -10429,7 +10631,8 @@
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr"/>
-      <c r="N152" s="4" t="inlineStr">
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" s="4" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -10497,7 +10700,8 @@
         </is>
       </c>
       <c r="M153" s="6" t="inlineStr"/>
-      <c r="N153" s="6" t="inlineStr">
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -10565,7 +10769,8 @@
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr"/>
-      <c r="N154" s="4" t="inlineStr">
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" s="4" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -10633,7 +10838,8 @@
         </is>
       </c>
       <c r="M155" s="6" t="inlineStr"/>
-      <c r="N155" s="6" t="inlineStr">
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" s="6" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -10701,7 +10907,8 @@
         </is>
       </c>
       <c r="M156" s="4" t="inlineStr"/>
-      <c r="N156" s="4" t="inlineStr">
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" s="4" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -10769,7 +10976,8 @@
         </is>
       </c>
       <c r="M157" s="6" t="inlineStr"/>
-      <c r="N157" s="6" t="inlineStr">
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" s="6" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
@@ -10837,7 +11045,8 @@
         </is>
       </c>
       <c r="M158" s="4" t="inlineStr"/>
-      <c r="N158" s="4" t="inlineStr">
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" s="4" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -10905,7 +11114,8 @@
         </is>
       </c>
       <c r="M159" s="6" t="inlineStr"/>
-      <c r="N159" s="6" t="inlineStr">
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" s="6" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
@@ -10973,7 +11183,8 @@
         </is>
       </c>
       <c r="M160" s="4" t="inlineStr"/>
-      <c r="N160" s="4" t="inlineStr">
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" s="4" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -11041,7 +11252,8 @@
         </is>
       </c>
       <c r="M161" s="6" t="inlineStr"/>
-      <c r="N161" s="6" t="inlineStr">
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -11109,7 +11321,8 @@
         </is>
       </c>
       <c r="M162" s="4" t="inlineStr"/>
-      <c r="N162" s="4" t="inlineStr">
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -11177,7 +11390,8 @@
         </is>
       </c>
       <c r="M163" s="6" t="inlineStr"/>
-      <c r="N163" s="6" t="inlineStr">
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -11245,7 +11459,8 @@
         </is>
       </c>
       <c r="M164" s="4" t="inlineStr"/>
-      <c r="N164" s="4" t="inlineStr">
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -11313,7 +11528,8 @@
         </is>
       </c>
       <c r="M165" s="6" t="inlineStr"/>
-      <c r="N165" s="6" t="inlineStr">
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" s="6" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
@@ -11381,7 +11597,8 @@
         </is>
       </c>
       <c r="M166" s="4" t="inlineStr"/>
-      <c r="N166" s="4" t="inlineStr">
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" s="4" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -11449,7 +11666,8 @@
         </is>
       </c>
       <c r="M167" s="6" t="inlineStr"/>
-      <c r="N167" s="6" t="inlineStr">
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" s="6" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -11517,7 +11735,8 @@
         </is>
       </c>
       <c r="M168" s="4" t="inlineStr"/>
-      <c r="N168" s="4" t="inlineStr">
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -11585,7 +11804,8 @@
         </is>
       </c>
       <c r="M169" s="6" t="inlineStr"/>
-      <c r="N169" s="6" t="inlineStr">
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -11653,7 +11873,8 @@
         </is>
       </c>
       <c r="M170" s="4" t="inlineStr"/>
-      <c r="N170" s="4" t="inlineStr">
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -11721,7 +11942,8 @@
         </is>
       </c>
       <c r="M171" s="6" t="inlineStr"/>
-      <c r="N171" s="6" t="inlineStr">
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" s="6" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
@@ -11789,7 +12011,8 @@
         </is>
       </c>
       <c r="M172" s="4" t="inlineStr"/>
-      <c r="N172" s="4" t="inlineStr">
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" s="4" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -11857,7 +12080,8 @@
         </is>
       </c>
       <c r="M173" s="6" t="inlineStr"/>
-      <c r="N173" s="6" t="inlineStr">
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" s="6" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -11925,7 +12149,8 @@
         </is>
       </c>
       <c r="M174" s="4" t="inlineStr"/>
-      <c r="N174" s="4" t="inlineStr">
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" s="4" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
@@ -11993,7 +12218,8 @@
         </is>
       </c>
       <c r="M175" s="6" t="inlineStr"/>
-      <c r="N175" s="6" t="inlineStr">
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -12061,7 +12287,8 @@
         </is>
       </c>
       <c r="M176" s="4" t="inlineStr"/>
-      <c r="N176" s="4" t="inlineStr">
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" s="4" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -12129,7 +12356,8 @@
         </is>
       </c>
       <c r="M177" s="6" t="inlineStr"/>
-      <c r="N177" s="6" t="inlineStr">
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" s="6" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
@@ -12197,7 +12425,8 @@
         </is>
       </c>
       <c r="M178" s="4" t="inlineStr"/>
-      <c r="N178" s="4" t="inlineStr">
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" s="4" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
@@ -12265,7 +12494,8 @@
         </is>
       </c>
       <c r="M179" s="6" t="inlineStr"/>
-      <c r="N179" s="6" t="inlineStr">
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -12333,7 +12563,8 @@
         </is>
       </c>
       <c r="M180" s="4" t="inlineStr"/>
-      <c r="N180" s="4" t="inlineStr">
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -12401,7 +12632,8 @@
         </is>
       </c>
       <c r="M181" s="6" t="inlineStr"/>
-      <c r="N181" s="6" t="inlineStr">
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" s="6" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -12469,7 +12701,8 @@
         </is>
       </c>
       <c r="M182" s="4" t="inlineStr"/>
-      <c r="N182" s="4" t="inlineStr">
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" s="4" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -12537,7 +12770,8 @@
         </is>
       </c>
       <c r="M183" s="6" t="inlineStr"/>
-      <c r="N183" s="6" t="inlineStr">
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" s="6" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -12605,7 +12839,8 @@
         </is>
       </c>
       <c r="M184" s="4" t="inlineStr"/>
-      <c r="N184" s="4" t="inlineStr">
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" s="4" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -12673,7 +12908,8 @@
         </is>
       </c>
       <c r="M185" s="6" t="inlineStr"/>
-      <c r="N185" s="6" t="inlineStr">
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -12741,7 +12977,8 @@
         </is>
       </c>
       <c r="M186" s="4" t="inlineStr"/>
-      <c r="N186" s="4" t="inlineStr">
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" s="4" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -12809,7 +13046,8 @@
         </is>
       </c>
       <c r="M187" s="6" t="inlineStr"/>
-      <c r="N187" s="6" t="inlineStr">
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" s="6" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
@@ -12877,7 +13115,8 @@
         </is>
       </c>
       <c r="M188" s="4" t="inlineStr"/>
-      <c r="N188" s="4" t="inlineStr">
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -12945,7 +13184,8 @@
         </is>
       </c>
       <c r="M189" s="6" t="inlineStr"/>
-      <c r="N189" s="6" t="inlineStr">
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" s="6" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
@@ -13013,7 +13253,8 @@
         </is>
       </c>
       <c r="M190" s="4" t="inlineStr"/>
-      <c r="N190" s="4" t="inlineStr">
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" s="4" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -13081,7 +13322,8 @@
         </is>
       </c>
       <c r="M191" s="6" t="inlineStr"/>
-      <c r="N191" s="6" t="inlineStr">
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" s="6" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -13149,7 +13391,8 @@
         </is>
       </c>
       <c r="M192" s="4" t="inlineStr"/>
-      <c r="N192" s="4" t="inlineStr">
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -13217,7 +13460,8 @@
         </is>
       </c>
       <c r="M193" s="6" t="inlineStr"/>
-      <c r="N193" s="6" t="inlineStr">
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -13285,7 +13529,8 @@
         </is>
       </c>
       <c r="M194" s="4" t="inlineStr"/>
-      <c r="N194" s="4" t="inlineStr">
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -13353,7 +13598,8 @@
         </is>
       </c>
       <c r="M195" s="6" t="inlineStr"/>
-      <c r="N195" s="6" t="inlineStr">
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -13421,7 +13667,8 @@
         </is>
       </c>
       <c r="M196" s="4" t="inlineStr"/>
-      <c r="N196" s="4" t="inlineStr">
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" s="4" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
@@ -13489,7 +13736,8 @@
         </is>
       </c>
       <c r="M197" s="6" t="inlineStr"/>
-      <c r="N197" s="6" t="inlineStr">
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" s="6" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
@@ -13557,7 +13805,8 @@
         </is>
       </c>
       <c r="M198" s="4" t="inlineStr"/>
-      <c r="N198" s="4" t="inlineStr">
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" s="4" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
@@ -13625,7 +13874,8 @@
         </is>
       </c>
       <c r="M199" s="6" t="inlineStr"/>
-      <c r="N199" s="6" t="inlineStr">
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -13693,7 +13943,8 @@
         </is>
       </c>
       <c r="M200" s="4" t="inlineStr"/>
-      <c r="N200" s="4" t="inlineStr">
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" s="4" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -13761,7 +14012,8 @@
         </is>
       </c>
       <c r="M201" s="6" t="inlineStr"/>
-      <c r="N201" s="6" t="inlineStr">
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" s="6" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
@@ -13829,7 +14081,8 @@
         </is>
       </c>
       <c r="M202" s="4" t="inlineStr"/>
-      <c r="N202" s="4" t="inlineStr">
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -13897,7 +14150,8 @@
         </is>
       </c>
       <c r="M203" s="6" t="inlineStr"/>
-      <c r="N203" s="6" t="inlineStr">
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -13965,7 +14219,8 @@
         </is>
       </c>
       <c r="M204" s="4" t="inlineStr"/>
-      <c r="N204" s="4" t="inlineStr">
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -14033,7 +14288,8 @@
         </is>
       </c>
       <c r="M205" s="6" t="inlineStr"/>
-      <c r="N205" s="6" t="inlineStr">
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -14101,7 +14357,8 @@
         </is>
       </c>
       <c r="M206" s="4" t="inlineStr"/>
-      <c r="N206" s="4" t="inlineStr">
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -14169,7 +14426,8 @@
         </is>
       </c>
       <c r="M207" s="6" t="inlineStr"/>
-      <c r="N207" s="6" t="inlineStr">
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" s="6" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
@@ -14237,7 +14495,8 @@
         </is>
       </c>
       <c r="M208" s="4" t="inlineStr"/>
-      <c r="N208" s="4" t="inlineStr">
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -14305,7 +14564,8 @@
         </is>
       </c>
       <c r="M209" s="6" t="inlineStr"/>
-      <c r="N209" s="6" t="inlineStr">
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -14373,7 +14633,8 @@
         </is>
       </c>
       <c r="M210" s="4" t="inlineStr"/>
-      <c r="N210" s="4" t="inlineStr">
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" s="4" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -14437,7 +14698,8 @@
       </c>
       <c r="L211" s="6" t="inlineStr"/>
       <c r="M211" s="6" t="inlineStr"/>
-      <c r="N211" s="6" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" s="6" t="inlineStr"/>
     </row>
     <row r="212" ht="24" customHeight="1">
       <c r="A212" s="3" t="inlineStr">
@@ -14493,7 +14755,8 @@
         </is>
       </c>
       <c r="M212" s="4" t="inlineStr"/>
-      <c r="N212" s="4" t="inlineStr">
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" s="4" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -14553,7 +14816,8 @@
         </is>
       </c>
       <c r="M213" s="6" t="inlineStr"/>
-      <c r="N213" s="6" t="inlineStr">
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" s="6" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -14613,7 +14877,8 @@
         </is>
       </c>
       <c r="M214" s="4" t="inlineStr"/>
-      <c r="N214" s="4" t="inlineStr">
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" s="4" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
@@ -14673,7 +14938,8 @@
         </is>
       </c>
       <c r="M215" s="6" t="inlineStr"/>
-      <c r="N215" s="6" t="inlineStr">
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" s="6" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
@@ -14733,7 +14999,8 @@
         </is>
       </c>
       <c r="M216" s="4" t="inlineStr"/>
-      <c r="N216" s="4" t="inlineStr">
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" s="4" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -14793,7 +15060,8 @@
         </is>
       </c>
       <c r="M217" s="6" t="inlineStr"/>
-      <c r="N217" s="6" t="inlineStr">
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" s="6" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
@@ -14853,7 +15121,8 @@
         </is>
       </c>
       <c r="M218" s="4" t="inlineStr"/>
-      <c r="N218" s="4" t="inlineStr">
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" s="4" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
@@ -14913,7 +15182,8 @@
         </is>
       </c>
       <c r="M219" s="6" t="inlineStr"/>
-      <c r="N219" s="6" t="inlineStr">
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" s="6" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -14973,7 +15243,8 @@
         </is>
       </c>
       <c r="M220" s="4" t="inlineStr"/>
-      <c r="N220" s="4" t="inlineStr">
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" s="4" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -15033,7 +15304,8 @@
         </is>
       </c>
       <c r="M221" s="6" t="inlineStr"/>
-      <c r="N221" s="6" t="inlineStr">
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" s="6" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
@@ -15093,7 +15365,8 @@
         </is>
       </c>
       <c r="M222" s="4" t="inlineStr"/>
-      <c r="N222" s="4" t="inlineStr">
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" s="4" t="inlineStr">
         <is>
           <t>8.8</t>
         </is>
@@ -15153,7 +15426,8 @@
         </is>
       </c>
       <c r="M223" s="6" t="inlineStr"/>
-      <c r="N223" s="6" t="inlineStr">
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" s="6" t="inlineStr">
         <is>
           <t>9.3</t>
         </is>
@@ -15213,7 +15487,8 @@
         </is>
       </c>
       <c r="M224" s="4" t="inlineStr"/>
-      <c r="N224" s="4" t="inlineStr">
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" s="4" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -15273,7 +15548,8 @@
         </is>
       </c>
       <c r="M225" s="6" t="inlineStr"/>
-      <c r="N225" s="6" t="inlineStr">
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" s="6" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -15333,7 +15609,8 @@
         </is>
       </c>
       <c r="M226" s="4" t="inlineStr"/>
-      <c r="N226" s="4" t="inlineStr">
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" s="4" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
@@ -15393,7 +15670,8 @@
         </is>
       </c>
       <c r="M227" s="6" t="inlineStr"/>
-      <c r="N227" s="6" t="inlineStr">
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -15453,7 +15731,8 @@
         </is>
       </c>
       <c r="M228" s="4" t="inlineStr"/>
-      <c r="N228" s="4" t="inlineStr">
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" s="4" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
@@ -15513,7 +15792,8 @@
         </is>
       </c>
       <c r="M229" s="6" t="inlineStr"/>
-      <c r="N229" s="6" t="inlineStr">
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" s="6" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
@@ -15573,7 +15853,8 @@
         </is>
       </c>
       <c r="M230" s="4" t="inlineStr"/>
-      <c r="N230" s="4" t="inlineStr">
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" s="4" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
@@ -15633,7 +15914,8 @@
         </is>
       </c>
       <c r="M231" s="6" t="inlineStr"/>
-      <c r="N231" s="6" t="inlineStr">
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" s="6" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
@@ -15693,7 +15975,8 @@
         </is>
       </c>
       <c r="M232" s="4" t="inlineStr"/>
-      <c r="N232" s="4" t="inlineStr">
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -15753,7 +16036,8 @@
         </is>
       </c>
       <c r="M233" s="6" t="inlineStr"/>
-      <c r="N233" s="6" t="inlineStr">
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" s="6" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -15813,7 +16097,8 @@
         </is>
       </c>
       <c r="M234" s="4" t="inlineStr"/>
-      <c r="N234" s="4" t="inlineStr">
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" s="4" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
@@ -15873,7 +16158,8 @@
         </is>
       </c>
       <c r="M235" s="6" t="inlineStr"/>
-      <c r="N235" s="6" t="inlineStr">
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -15933,7 +16219,8 @@
         </is>
       </c>
       <c r="M236" s="4" t="inlineStr"/>
-      <c r="N236" s="4" t="inlineStr">
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -15993,7 +16280,8 @@
         </is>
       </c>
       <c r="M237" s="6" t="inlineStr"/>
-      <c r="N237" s="6" t="inlineStr">
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -16053,7 +16341,8 @@
         </is>
       </c>
       <c r="M238" s="4" t="inlineStr"/>
-      <c r="N238" s="4" t="inlineStr">
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -16113,7 +16402,8 @@
         </is>
       </c>
       <c r="M239" s="6" t="inlineStr"/>
-      <c r="N239" s="6" t="inlineStr">
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -16173,7 +16463,8 @@
         </is>
       </c>
       <c r="M240" s="4" t="inlineStr"/>
-      <c r="N240" s="4" t="inlineStr">
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" s="4" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -16233,7 +16524,8 @@
         </is>
       </c>
       <c r="M241" s="6" t="inlineStr"/>
-      <c r="N241" s="6" t="inlineStr">
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -16293,7 +16585,8 @@
         </is>
       </c>
       <c r="M242" s="4" t="inlineStr"/>
-      <c r="N242" s="4" t="inlineStr">
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" s="4" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -16353,7 +16646,8 @@
         </is>
       </c>
       <c r="M243" s="6" t="inlineStr"/>
-      <c r="N243" s="6" t="inlineStr">
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" s="6" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -16413,7 +16707,8 @@
         </is>
       </c>
       <c r="M244" s="4" t="inlineStr"/>
-      <c r="N244" s="4" t="inlineStr">
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -16473,7 +16768,8 @@
         </is>
       </c>
       <c r="M245" s="6" t="inlineStr"/>
-      <c r="N245" s="6" t="inlineStr">
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -16533,7 +16829,8 @@
         </is>
       </c>
       <c r="M246" s="4" t="inlineStr"/>
-      <c r="N246" s="4" t="inlineStr">
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -16593,7 +16890,8 @@
         </is>
       </c>
       <c r="M247" s="6" t="inlineStr"/>
-      <c r="N247" s="6" t="inlineStr">
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -16653,7 +16951,8 @@
         </is>
       </c>
       <c r="M248" s="4" t="inlineStr"/>
-      <c r="N248" s="4" t="inlineStr">
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -16713,7 +17012,8 @@
         </is>
       </c>
       <c r="M249" s="6" t="inlineStr"/>
-      <c r="N249" s="6" t="inlineStr">
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" s="6" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -16773,7 +17073,8 @@
         </is>
       </c>
       <c r="M250" s="4" t="inlineStr"/>
-      <c r="N250" s="4" t="inlineStr">
+      <c r="N250" t="inlineStr"/>
+      <c r="O250" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -16833,7 +17134,8 @@
         </is>
       </c>
       <c r="M251" s="6" t="inlineStr"/>
-      <c r="N251" s="6" t="inlineStr">
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" s="6" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -16893,7 +17195,8 @@
         </is>
       </c>
       <c r="M252" s="4" t="inlineStr"/>
-      <c r="N252" s="4" t="inlineStr">
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" s="4" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -16953,7 +17256,8 @@
         </is>
       </c>
       <c r="M253" s="6" t="inlineStr"/>
-      <c r="N253" s="6" t="inlineStr">
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" s="6" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -17013,7 +17317,8 @@
         </is>
       </c>
       <c r="M254" s="4" t="inlineStr"/>
-      <c r="N254" s="4" t="inlineStr">
+      <c r="N254" t="inlineStr"/>
+      <c r="O254" s="4" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -17073,7 +17378,8 @@
         </is>
       </c>
       <c r="M255" s="6" t="inlineStr"/>
-      <c r="N255" s="6" t="inlineStr">
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -17133,7 +17439,8 @@
         </is>
       </c>
       <c r="M256" s="4" t="inlineStr"/>
-      <c r="N256" s="4" t="inlineStr">
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -17193,7 +17500,8 @@
         </is>
       </c>
       <c r="M257" s="6" t="inlineStr"/>
-      <c r="N257" s="6" t="inlineStr">
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -17253,7 +17561,8 @@
         </is>
       </c>
       <c r="M258" s="4" t="inlineStr"/>
-      <c r="N258" s="4" t="inlineStr">
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -17313,7 +17622,8 @@
         </is>
       </c>
       <c r="M259" s="6" t="inlineStr"/>
-      <c r="N259" s="6" t="inlineStr">
+      <c r="N259" t="inlineStr"/>
+      <c r="O259" s="6" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -17373,7 +17683,8 @@
         </is>
       </c>
       <c r="M260" s="4" t="inlineStr"/>
-      <c r="N260" s="4" t="inlineStr">
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -17433,7 +17744,8 @@
         </is>
       </c>
       <c r="M261" s="6" t="inlineStr"/>
-      <c r="N261" s="6" t="inlineStr">
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -17493,7 +17805,8 @@
         </is>
       </c>
       <c r="M262" s="4" t="inlineStr"/>
-      <c r="N262" s="4" t="inlineStr">
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" s="4" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -17553,7 +17866,8 @@
         </is>
       </c>
       <c r="M263" s="6" t="inlineStr"/>
-      <c r="N263" s="6" t="inlineStr">
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" s="6" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -17613,7 +17927,8 @@
         </is>
       </c>
       <c r="M264" s="4" t="inlineStr"/>
-      <c r="N264" s="4" t="inlineStr">
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -17673,7 +17988,8 @@
         </is>
       </c>
       <c r="M265" s="6" t="inlineStr"/>
-      <c r="N265" s="6" t="inlineStr">
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" s="6" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -17733,7 +18049,8 @@
         </is>
       </c>
       <c r="M266" s="4" t="inlineStr"/>
-      <c r="N266" s="4" t="inlineStr">
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -17793,7 +18110,8 @@
         </is>
       </c>
       <c r="M267" s="6" t="inlineStr"/>
-      <c r="N267" s="6" t="inlineStr">
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -17853,7 +18171,8 @@
         </is>
       </c>
       <c r="M268" s="4" t="inlineStr"/>
-      <c r="N268" s="4" t="inlineStr">
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -17913,7 +18232,8 @@
         </is>
       </c>
       <c r="M269" s="6" t="inlineStr"/>
-      <c r="N269" s="6" t="inlineStr">
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -17973,7 +18293,8 @@
         </is>
       </c>
       <c r="M270" s="4" t="inlineStr"/>
-      <c r="N270" s="4" t="inlineStr">
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -18033,7 +18354,8 @@
         </is>
       </c>
       <c r="M271" s="6" t="inlineStr"/>
-      <c r="N271" s="6" t="inlineStr">
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" s="6" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -18093,7 +18415,8 @@
         </is>
       </c>
       <c r="M272" s="4" t="inlineStr"/>
-      <c r="N272" s="4" t="inlineStr">
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -18153,7 +18476,8 @@
         </is>
       </c>
       <c r="M273" s="6" t="inlineStr"/>
-      <c r="N273" s="6" t="inlineStr">
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" s="6" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -18213,7 +18537,8 @@
         </is>
       </c>
       <c r="M274" s="4" t="inlineStr"/>
-      <c r="N274" s="4" t="inlineStr">
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -18273,7 +18598,8 @@
         </is>
       </c>
       <c r="M275" s="6" t="inlineStr"/>
-      <c r="N275" s="6" t="inlineStr">
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -18333,7 +18659,8 @@
         </is>
       </c>
       <c r="M276" s="4" t="inlineStr"/>
-      <c r="N276" s="4" t="inlineStr">
+      <c r="N276" t="inlineStr"/>
+      <c r="O276" s="4" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -18393,7 +18720,8 @@
         </is>
       </c>
       <c r="M277" s="6" t="inlineStr"/>
-      <c r="N277" s="6" t="inlineStr">
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" s="6" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -18453,7 +18781,8 @@
         </is>
       </c>
       <c r="M278" s="4" t="inlineStr"/>
-      <c r="N278" s="4" t="inlineStr">
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" s="4" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -18513,7 +18842,8 @@
         </is>
       </c>
       <c r="M279" s="6" t="inlineStr"/>
-      <c r="N279" s="6" t="inlineStr">
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -18573,7 +18903,8 @@
         </is>
       </c>
       <c r="M280" s="4" t="inlineStr"/>
-      <c r="N280" s="4" t="inlineStr">
+      <c r="N280" t="inlineStr"/>
+      <c r="O280" s="4" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -18633,7 +18964,8 @@
         </is>
       </c>
       <c r="M281" s="6" t="inlineStr"/>
-      <c r="N281" s="6" t="inlineStr">
+      <c r="N281" t="inlineStr"/>
+      <c r="O281" s="6" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -18693,7 +19025,8 @@
         </is>
       </c>
       <c r="M282" s="4" t="inlineStr"/>
-      <c r="N282" s="4" t="inlineStr">
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" s="4" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -18753,7 +19086,8 @@
         </is>
       </c>
       <c r="M283" s="6" t="inlineStr"/>
-      <c r="N283" s="6" t="inlineStr">
+      <c r="N283" t="inlineStr"/>
+      <c r="O283" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -18813,7 +19147,8 @@
         </is>
       </c>
       <c r="M284" s="4" t="inlineStr"/>
-      <c r="N284" s="4" t="inlineStr">
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -18873,7 +19208,8 @@
         </is>
       </c>
       <c r="M285" s="6" t="inlineStr"/>
-      <c r="N285" s="6" t="inlineStr">
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -18933,7 +19269,8 @@
         </is>
       </c>
       <c r="M286" s="4" t="inlineStr"/>
-      <c r="N286" s="4" t="inlineStr">
+      <c r="N286" t="inlineStr"/>
+      <c r="O286" s="4" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
@@ -18993,7 +19330,8 @@
         </is>
       </c>
       <c r="M287" s="6" t="inlineStr"/>
-      <c r="N287" s="6" t="inlineStr">
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" s="6" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
@@ -19053,7 +19391,8 @@
         </is>
       </c>
       <c r="M288" s="4" t="inlineStr"/>
-      <c r="N288" s="4" t="inlineStr">
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -19113,7 +19452,8 @@
         </is>
       </c>
       <c r="M289" s="6" t="inlineStr"/>
-      <c r="N289" s="6" t="inlineStr">
+      <c r="N289" t="inlineStr"/>
+      <c r="O289" s="6" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -19173,7 +19513,8 @@
         </is>
       </c>
       <c r="M290" s="4" t="inlineStr"/>
-      <c r="N290" s="4" t="inlineStr">
+      <c r="N290" t="inlineStr"/>
+      <c r="O290" s="4" t="inlineStr">
         <is>
           <t>8.8</t>
         </is>
@@ -19233,7 +19574,8 @@
         </is>
       </c>
       <c r="M291" s="6" t="inlineStr"/>
-      <c r="N291" s="6" t="inlineStr">
+      <c r="N291" t="inlineStr"/>
+      <c r="O291" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -19293,7 +19635,8 @@
         </is>
       </c>
       <c r="M292" s="4" t="inlineStr"/>
-      <c r="N292" s="4" t="inlineStr">
+      <c r="N292" t="inlineStr"/>
+      <c r="O292" s="4" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -19353,7 +19696,8 @@
         </is>
       </c>
       <c r="M293" s="6" t="inlineStr"/>
-      <c r="N293" s="6" t="inlineStr">
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" s="6" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -19413,7 +19757,8 @@
         </is>
       </c>
       <c r="M294" s="4" t="inlineStr"/>
-      <c r="N294" s="4" t="inlineStr">
+      <c r="N294" t="inlineStr"/>
+      <c r="O294" s="4" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -19473,7 +19818,8 @@
         </is>
       </c>
       <c r="M295" s="6" t="inlineStr"/>
-      <c r="N295" s="6" t="inlineStr">
+      <c r="N295" t="inlineStr"/>
+      <c r="O295" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -19533,7 +19879,8 @@
         </is>
       </c>
       <c r="M296" s="4" t="inlineStr"/>
-      <c r="N296" s="4" t="inlineStr">
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" s="4" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -19593,7 +19940,8 @@
         </is>
       </c>
       <c r="M297" s="6" t="inlineStr"/>
-      <c r="N297" s="6" t="inlineStr">
+      <c r="N297" t="inlineStr"/>
+      <c r="O297" s="6" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
@@ -19653,7 +20001,8 @@
         </is>
       </c>
       <c r="M298" s="4" t="inlineStr"/>
-      <c r="N298" s="4" t="inlineStr">
+      <c r="N298" t="inlineStr"/>
+      <c r="O298" s="4" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -19713,7 +20062,8 @@
         </is>
       </c>
       <c r="M299" s="6" t="inlineStr"/>
-      <c r="N299" s="6" t="inlineStr">
+      <c r="N299" t="inlineStr"/>
+      <c r="O299" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -19773,7 +20123,8 @@
         </is>
       </c>
       <c r="M300" s="4" t="inlineStr"/>
-      <c r="N300" s="4" t="inlineStr">
+      <c r="N300" t="inlineStr"/>
+      <c r="O300" s="4" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -19833,7 +20184,8 @@
         </is>
       </c>
       <c r="M301" s="6" t="inlineStr"/>
-      <c r="N301" s="6" t="inlineStr">
+      <c r="N301" t="inlineStr"/>
+      <c r="O301" s="6" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -19893,7 +20245,8 @@
         </is>
       </c>
       <c r="M302" s="4" t="inlineStr"/>
-      <c r="N302" s="4" t="inlineStr">
+      <c r="N302" t="inlineStr"/>
+      <c r="O302" s="4" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -19953,7 +20306,8 @@
         </is>
       </c>
       <c r="M303" s="6" t="inlineStr"/>
-      <c r="N303" s="6" t="inlineStr">
+      <c r="N303" t="inlineStr"/>
+      <c r="O303" s="6" t="inlineStr">
         <is>
           <t>9.1</t>
         </is>
@@ -20013,7 +20367,8 @@
         </is>
       </c>
       <c r="M304" s="4" t="inlineStr"/>
-      <c r="N304" s="4" t="inlineStr">
+      <c r="N304" t="inlineStr"/>
+      <c r="O304" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -20073,7 +20428,8 @@
         </is>
       </c>
       <c r="M305" s="6" t="inlineStr"/>
-      <c r="N305" s="6" t="inlineStr">
+      <c r="N305" t="inlineStr"/>
+      <c r="O305" s="6" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -20133,7 +20489,8 @@
         </is>
       </c>
       <c r="M306" s="4" t="inlineStr"/>
-      <c r="N306" s="4" t="inlineStr">
+      <c r="N306" t="inlineStr"/>
+      <c r="O306" s="4" t="inlineStr">
         <is>
           <t>8.9</t>
         </is>
@@ -20193,7 +20550,8 @@
         </is>
       </c>
       <c r="M307" s="6" t="inlineStr"/>
-      <c r="N307" s="6" t="inlineStr">
+      <c r="N307" t="inlineStr"/>
+      <c r="O307" s="6" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -20253,7 +20611,8 @@
         </is>
       </c>
       <c r="M308" s="4" t="inlineStr"/>
-      <c r="N308" s="4" t="inlineStr">
+      <c r="N308" t="inlineStr"/>
+      <c r="O308" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -20313,7 +20672,8 @@
         </is>
       </c>
       <c r="M309" s="6" t="inlineStr"/>
-      <c r="N309" s="6" t="inlineStr">
+      <c r="N309" t="inlineStr"/>
+      <c r="O309" s="6" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
@@ -20373,7 +20733,8 @@
         </is>
       </c>
       <c r="M310" s="4" t="inlineStr"/>
-      <c r="N310" s="4" t="inlineStr">
+      <c r="N310" t="inlineStr"/>
+      <c r="O310" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -20433,7 +20794,8 @@
         </is>
       </c>
       <c r="M311" s="6" t="inlineStr"/>
-      <c r="N311" s="6" t="inlineStr">
+      <c r="N311" t="inlineStr"/>
+      <c r="O311" s="6" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -20493,7 +20855,8 @@
         </is>
       </c>
       <c r="M312" s="4" t="inlineStr"/>
-      <c r="N312" s="4" t="inlineStr">
+      <c r="N312" t="inlineStr"/>
+      <c r="O312" s="4" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -20553,7 +20916,8 @@
         </is>
       </c>
       <c r="M313" s="6" t="inlineStr"/>
-      <c r="N313" s="6" t="inlineStr">
+      <c r="N313" t="inlineStr"/>
+      <c r="O313" s="6" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -20613,7 +20977,8 @@
         </is>
       </c>
       <c r="M314" s="4" t="inlineStr"/>
-      <c r="N314" s="4" t="inlineStr">
+      <c r="N314" t="inlineStr"/>
+      <c r="O314" s="4" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -20673,7 +21038,8 @@
         </is>
       </c>
       <c r="M315" s="6" t="inlineStr"/>
-      <c r="N315" s="6" t="inlineStr">
+      <c r="N315" t="inlineStr"/>
+      <c r="O315" s="6" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -20733,7 +21099,8 @@
         </is>
       </c>
       <c r="M316" s="4" t="inlineStr"/>
-      <c r="N316" s="4" t="inlineStr">
+      <c r="N316" t="inlineStr"/>
+      <c r="O316" s="4" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -20793,7 +21160,8 @@
         </is>
       </c>
       <c r="M317" s="6" t="inlineStr"/>
-      <c r="N317" s="6" t="inlineStr">
+      <c r="N317" t="inlineStr"/>
+      <c r="O317" s="6" t="inlineStr">
         <is>
           <t>9.9</t>
         </is>
@@ -20853,7 +21221,8 @@
         </is>
       </c>
       <c r="M318" s="4" t="inlineStr"/>
-      <c r="N318" s="4" t="inlineStr">
+      <c r="N318" t="inlineStr"/>
+      <c r="O318" s="4" t="inlineStr">
         <is>
           <t>9.9</t>
         </is>
@@ -20913,7 +21282,8 @@
         </is>
       </c>
       <c r="M319" s="6" t="inlineStr"/>
-      <c r="N319" s="6" t="inlineStr">
+      <c r="N319" t="inlineStr"/>
+      <c r="O319" s="6" t="inlineStr">
         <is>
           <t>9.7</t>
         </is>
@@ -20973,7 +21343,8 @@
         </is>
       </c>
       <c r="M320" s="4" t="inlineStr"/>
-      <c r="N320" s="4" t="inlineStr">
+      <c r="N320" t="inlineStr"/>
+      <c r="O320" s="4" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
@@ -21033,7 +21404,8 @@
         </is>
       </c>
       <c r="M321" s="6" t="inlineStr"/>
-      <c r="N321" s="6" t="inlineStr">
+      <c r="N321" t="inlineStr"/>
+      <c r="O321" s="6" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
@@ -21093,7 +21465,8 @@
         </is>
       </c>
       <c r="M322" s="4" t="inlineStr"/>
-      <c r="N322" s="4" t="inlineStr">
+      <c r="N322" t="inlineStr"/>
+      <c r="O322" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -21153,7 +21526,8 @@
         </is>
       </c>
       <c r="M323" s="6" t="inlineStr"/>
-      <c r="N323" s="6" t="inlineStr">
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" s="6" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
@@ -21213,7 +21587,8 @@
         </is>
       </c>
       <c r="M324" s="4" t="inlineStr"/>
-      <c r="N324" s="4" t="inlineStr">
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" s="4" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -21273,7 +21648,8 @@
         </is>
       </c>
       <c r="M325" s="6" t="inlineStr"/>
-      <c r="N325" s="6" t="inlineStr">
+      <c r="N325" t="inlineStr"/>
+      <c r="O325" s="6" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
@@ -21333,7 +21709,8 @@
         </is>
       </c>
       <c r="M326" s="4" t="inlineStr"/>
-      <c r="N326" s="4" t="inlineStr">
+      <c r="N326" t="inlineStr"/>
+      <c r="O326" s="4" t="inlineStr">
         <is>
           <t>11.6</t>
         </is>
@@ -21393,7 +21770,8 @@
         </is>
       </c>
       <c r="M327" s="6" t="inlineStr"/>
-      <c r="N327" s="6" t="inlineStr">
+      <c r="N327" t="inlineStr"/>
+      <c r="O327" s="6" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
@@ -21453,7 +21831,8 @@
         </is>
       </c>
       <c r="M328" s="4" t="inlineStr"/>
-      <c r="N328" s="4" t="inlineStr">
+      <c r="N328" t="inlineStr"/>
+      <c r="O328" s="4" t="inlineStr">
         <is>
           <t>11.6</t>
         </is>
@@ -21513,7 +21892,8 @@
         </is>
       </c>
       <c r="M329" s="6" t="inlineStr"/>
-      <c r="N329" s="6" t="inlineStr">
+      <c r="N329" t="inlineStr"/>
+      <c r="O329" s="6" t="inlineStr">
         <is>
           <t>11.5</t>
         </is>
@@ -21573,7 +21953,8 @@
         </is>
       </c>
       <c r="M330" s="4" t="inlineStr"/>
-      <c r="N330" s="4" t="inlineStr">
+      <c r="N330" t="inlineStr"/>
+      <c r="O330" s="4" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
@@ -21633,7 +22014,8 @@
         </is>
       </c>
       <c r="M331" s="6" t="inlineStr"/>
-      <c r="N331" s="6" t="inlineStr">
+      <c r="N331" t="inlineStr"/>
+      <c r="O331" s="6" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
@@ -21693,7 +22075,8 @@
         </is>
       </c>
       <c r="M332" s="4" t="inlineStr"/>
-      <c r="N332" s="4" t="inlineStr">
+      <c r="N332" t="inlineStr"/>
+      <c r="O332" s="4" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -21753,7 +22136,8 @@
         </is>
       </c>
       <c r="M333" s="6" t="inlineStr"/>
-      <c r="N333" s="6" t="inlineStr">
+      <c r="N333" t="inlineStr"/>
+      <c r="O333" s="6" t="inlineStr">
         <is>
           <t>8.9</t>
         </is>
@@ -21813,7 +22197,8 @@
         </is>
       </c>
       <c r="M334" s="4" t="inlineStr"/>
-      <c r="N334" s="4" t="inlineStr">
+      <c r="N334" t="inlineStr"/>
+      <c r="O334" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -21873,7 +22258,8 @@
         </is>
       </c>
       <c r="M335" s="6" t="inlineStr"/>
-      <c r="N335" s="6" t="inlineStr">
+      <c r="N335" t="inlineStr"/>
+      <c r="O335" s="6" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -21933,7 +22319,8 @@
         </is>
       </c>
       <c r="M336" s="4" t="inlineStr"/>
-      <c r="N336" s="4" t="inlineStr">
+      <c r="N336" t="inlineStr"/>
+      <c r="O336" s="4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -21993,7 +22380,8 @@
         </is>
       </c>
       <c r="M337" s="6" t="inlineStr"/>
-      <c r="N337" s="6" t="inlineStr">
+      <c r="N337" t="inlineStr"/>
+      <c r="O337" s="6" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
@@ -22053,7 +22441,8 @@
         </is>
       </c>
       <c r="M338" s="4" t="inlineStr"/>
-      <c r="N338" s="4" t="inlineStr">
+      <c r="N338" t="inlineStr"/>
+      <c r="O338" s="4" t="inlineStr">
         <is>
           <t>9.3</t>
         </is>
@@ -22113,7 +22502,8 @@
         </is>
       </c>
       <c r="M339" s="6" t="inlineStr"/>
-      <c r="N339" s="6" t="inlineStr">
+      <c r="N339" t="inlineStr"/>
+      <c r="O339" s="6" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -22173,7 +22563,8 @@
         </is>
       </c>
       <c r="M340" s="4" t="inlineStr"/>
-      <c r="N340" s="4" t="inlineStr">
+      <c r="N340" t="inlineStr"/>
+      <c r="O340" s="4" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
@@ -22233,7 +22624,8 @@
         </is>
       </c>
       <c r="M341" s="6" t="inlineStr"/>
-      <c r="N341" s="6" t="inlineStr">
+      <c r="N341" t="inlineStr"/>
+      <c r="O341" s="6" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
@@ -22293,7 +22685,8 @@
         </is>
       </c>
       <c r="M342" s="4" t="inlineStr"/>
-      <c r="N342" s="4" t="inlineStr">
+      <c r="N342" t="inlineStr"/>
+      <c r="O342" s="4" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
@@ -22353,7 +22746,8 @@
         </is>
       </c>
       <c r="M343" s="6" t="inlineStr"/>
-      <c r="N343" s="6" t="inlineStr">
+      <c r="N343" t="inlineStr"/>
+      <c r="O343" s="6" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -22413,7 +22807,8 @@
         </is>
       </c>
       <c r="M344" s="4" t="inlineStr"/>
-      <c r="N344" s="4" t="inlineStr">
+      <c r="N344" t="inlineStr"/>
+      <c r="O344" s="4" t="inlineStr">
         <is>
           <t>11.7</t>
         </is>
@@ -22473,7 +22868,8 @@
         </is>
       </c>
       <c r="M345" s="6" t="inlineStr"/>
-      <c r="N345" s="6" t="inlineStr">
+      <c r="N345" t="inlineStr"/>
+      <c r="O345" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -22533,7 +22929,8 @@
         </is>
       </c>
       <c r="M346" s="4" t="inlineStr"/>
-      <c r="N346" s="4" t="inlineStr">
+      <c r="N346" t="inlineStr"/>
+      <c r="O346" s="4" t="inlineStr">
         <is>
           <t>9.1</t>
         </is>
@@ -22593,7 +22990,8 @@
         </is>
       </c>
       <c r="M347" s="6" t="inlineStr"/>
-      <c r="N347" s="6" t="inlineStr">
+      <c r="N347" t="inlineStr"/>
+      <c r="O347" s="6" t="inlineStr">
         <is>
           <t>9.8</t>
         </is>
@@ -22648,8 +23046,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M348" s="4" t="inlineStr"/>
-      <c r="N348" s="4" t="inlineStr">
+      <c r="M348" s="4" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr"/>
+      <c r="O348" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -22704,8 +23107,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M349" s="6" t="inlineStr"/>
-      <c r="N349" s="6" t="inlineStr">
+      <c r="M349" s="6" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr"/>
+      <c r="O349" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -22760,8 +23168,13 @@
           <t>0</t>
         </is>
       </c>
-      <c r="M350" s="4" t="inlineStr"/>
-      <c r="N350" s="4" t="inlineStr">
+      <c r="M350" s="4" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr"/>
+      <c r="O350" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -22817,7 +23230,8 @@
         </is>
       </c>
       <c r="M351" s="6" t="inlineStr"/>
-      <c r="N351" s="6" t="inlineStr">
+      <c r="N351" t="inlineStr"/>
+      <c r="O351" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -22873,7 +23287,8 @@
         </is>
       </c>
       <c r="M352" s="4" t="inlineStr"/>
-      <c r="N352" s="4" t="inlineStr">
+      <c r="N352" t="inlineStr"/>
+      <c r="O352" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -22929,7 +23344,8 @@
         </is>
       </c>
       <c r="M353" s="6" t="inlineStr"/>
-      <c r="N353" s="6" t="inlineStr">
+      <c r="N353" t="inlineStr"/>
+      <c r="O353" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -22981,7 +23397,8 @@
       </c>
       <c r="L354" s="4" t="inlineStr"/>
       <c r="M354" s="4" t="inlineStr"/>
-      <c r="N354" s="4" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
+      <c r="O354" s="4" t="inlineStr"/>
     </row>
     <row r="355" ht="48" customHeight="1">
       <c r="A355" s="5" t="inlineStr">
@@ -23033,7 +23450,8 @@
         </is>
       </c>
       <c r="M355" s="6" t="inlineStr"/>
-      <c r="N355" s="6" t="inlineStr">
+      <c r="N355" t="inlineStr"/>
+      <c r="O355" s="6" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -23089,7 +23507,8 @@
         </is>
       </c>
       <c r="M356" s="4" t="inlineStr"/>
-      <c r="N356" s="4" t="inlineStr">
+      <c r="N356" t="inlineStr"/>
+      <c r="O356" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -23141,7 +23560,8 @@
       </c>
       <c r="L357" s="6" t="inlineStr"/>
       <c r="M357" s="6" t="inlineStr"/>
-      <c r="N357" s="6" t="inlineStr"/>
+      <c r="N357" t="inlineStr"/>
+      <c r="O357" s="6" t="inlineStr"/>
     </row>
     <row r="358" ht="32" customHeight="1">
       <c r="A358" s="3" t="inlineStr">
@@ -23193,7 +23613,8 @@
         </is>
       </c>
       <c r="M358" s="4" t="inlineStr"/>
-      <c r="N358" s="4" t="inlineStr">
+      <c r="N358" t="inlineStr"/>
+      <c r="O358" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -23245,7 +23666,8 @@
       </c>
       <c r="L359" s="6" t="inlineStr"/>
       <c r="M359" s="6" t="inlineStr"/>
-      <c r="N359" s="6" t="inlineStr"/>
+      <c r="N359" t="inlineStr"/>
+      <c r="O359" s="6" t="inlineStr"/>
     </row>
     <row r="360" ht="32" customHeight="1">
       <c r="A360" s="3" t="inlineStr">
@@ -23293,7 +23715,8 @@
       </c>
       <c r="L360" s="4" t="inlineStr"/>
       <c r="M360" s="4" t="inlineStr"/>
-      <c r="N360" s="4" t="inlineStr"/>
+      <c r="N360" t="inlineStr"/>
+      <c r="O360" s="4" t="inlineStr"/>
     </row>
     <row r="361" ht="32" customHeight="1">
       <c r="A361" s="5" t="inlineStr">
@@ -23345,7 +23768,8 @@
         </is>
       </c>
       <c r="M361" s="6" t="inlineStr"/>
-      <c r="N361" s="6" t="inlineStr">
+      <c r="N361" t="inlineStr"/>
+      <c r="O361" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -23397,7 +23821,8 @@
       </c>
       <c r="L362" s="4" t="inlineStr"/>
       <c r="M362" s="4" t="inlineStr"/>
-      <c r="N362" s="4" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
+      <c r="O362" s="4" t="inlineStr"/>
     </row>
     <row r="363" ht="32" customHeight="1">
       <c r="A363" s="5" t="inlineStr">
@@ -23445,7 +23870,8 @@
       </c>
       <c r="L363" s="6" t="inlineStr"/>
       <c r="M363" s="6" t="inlineStr"/>
-      <c r="N363" s="6" t="inlineStr"/>
+      <c r="N363" t="inlineStr"/>
+      <c r="O363" s="6" t="inlineStr"/>
     </row>
     <row r="364" ht="32" customHeight="1">
       <c r="A364" s="3" t="inlineStr">
@@ -23493,7 +23919,8 @@
       </c>
       <c r="L364" s="4" t="inlineStr"/>
       <c r="M364" s="4" t="inlineStr"/>
-      <c r="N364" s="4" t="inlineStr"/>
+      <c r="N364" t="inlineStr"/>
+      <c r="O364" s="4" t="inlineStr"/>
     </row>
     <row r="365" ht="32" customHeight="1">
       <c r="A365" s="5" t="inlineStr">
@@ -23545,7 +23972,8 @@
         </is>
       </c>
       <c r="M365" s="6" t="inlineStr"/>
-      <c r="N365" s="6" t="inlineStr">
+      <c r="N365" t="inlineStr"/>
+      <c r="O365" s="6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -23601,7 +24029,8 @@
         </is>
       </c>
       <c r="M366" s="4" t="inlineStr"/>
-      <c r="N366" s="4" t="inlineStr">
+      <c r="N366" t="inlineStr"/>
+      <c r="O366" s="4" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
@@ -23653,7 +24082,8 @@
       </c>
       <c r="L367" s="6" t="inlineStr"/>
       <c r="M367" s="6" t="inlineStr"/>
-      <c r="N367" s="6" t="inlineStr"/>
+      <c r="N367" t="inlineStr"/>
+      <c r="O367" s="6" t="inlineStr"/>
     </row>
     <row r="368" ht="32" customHeight="1">
       <c r="A368" s="3" t="inlineStr">
@@ -23705,7 +24135,8 @@
         </is>
       </c>
       <c r="M368" s="4" t="inlineStr"/>
-      <c r="N368" s="4" t="inlineStr">
+      <c r="N368" t="inlineStr"/>
+      <c r="O368" s="4" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -23761,7 +24192,8 @@
         </is>
       </c>
       <c r="M369" s="6" t="inlineStr"/>
-      <c r="N369" s="6" t="inlineStr">
+      <c r="N369" t="inlineStr"/>
+      <c r="O369" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -23817,7 +24249,8 @@
         </is>
       </c>
       <c r="M370" s="4" t="inlineStr"/>
-      <c r="N370" s="4" t="inlineStr">
+      <c r="N370" t="inlineStr"/>
+      <c r="O370" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -23869,7 +24302,8 @@
       </c>
       <c r="L371" s="6" t="inlineStr"/>
       <c r="M371" s="6" t="inlineStr"/>
-      <c r="N371" s="6" t="inlineStr"/>
+      <c r="N371" t="inlineStr"/>
+      <c r="O371" s="6" t="inlineStr"/>
     </row>
     <row r="372" ht="32" customHeight="1">
       <c r="A372" s="3" t="inlineStr">
@@ -23917,7 +24351,8 @@
       </c>
       <c r="L372" s="4" t="inlineStr"/>
       <c r="M372" s="4" t="inlineStr"/>
-      <c r="N372" s="4" t="inlineStr"/>
+      <c r="N372" t="inlineStr"/>
+      <c r="O372" s="4" t="inlineStr"/>
     </row>
     <row r="373" ht="32" customHeight="1">
       <c r="A373" s="5" t="inlineStr">
@@ -23965,7 +24400,8 @@
       </c>
       <c r="L373" s="6" t="inlineStr"/>
       <c r="M373" s="6" t="inlineStr"/>
-      <c r="N373" s="6" t="inlineStr"/>
+      <c r="N373" t="inlineStr"/>
+      <c r="O373" s="6" t="inlineStr"/>
     </row>
     <row r="374" ht="32" customHeight="1">
       <c r="A374" s="3" t="inlineStr">
@@ -24013,7 +24449,8 @@
       </c>
       <c r="L374" s="4" t="inlineStr"/>
       <c r="M374" s="4" t="inlineStr"/>
-      <c r="N374" s="4" t="inlineStr"/>
+      <c r="N374" t="inlineStr"/>
+      <c r="O374" s="4" t="inlineStr"/>
     </row>
     <row r="375" ht="32" customHeight="1">
       <c r="A375" s="5" t="inlineStr">
@@ -24061,7 +24498,8 @@
       </c>
       <c r="L375" s="6" t="inlineStr"/>
       <c r="M375" s="6" t="inlineStr"/>
-      <c r="N375" s="6" t="inlineStr"/>
+      <c r="N375" t="inlineStr"/>
+      <c r="O375" s="6" t="inlineStr"/>
     </row>
     <row r="376" ht="32" customHeight="1">
       <c r="A376" s="3" t="inlineStr">
@@ -24113,7 +24551,8 @@
         </is>
       </c>
       <c r="M376" s="4" t="inlineStr"/>
-      <c r="N376" s="4" t="inlineStr">
+      <c r="N376" t="inlineStr"/>
+      <c r="O376" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -24165,7 +24604,8 @@
       </c>
       <c r="L377" s="6" t="inlineStr"/>
       <c r="M377" s="6" t="inlineStr"/>
-      <c r="N377" s="6" t="inlineStr"/>
+      <c r="N377" t="inlineStr"/>
+      <c r="O377" s="6" t="inlineStr"/>
     </row>
     <row r="378" ht="32" customHeight="1">
       <c r="A378" s="3" t="inlineStr">
@@ -24213,7 +24653,8 @@
       </c>
       <c r="L378" s="4" t="inlineStr"/>
       <c r="M378" s="4" t="inlineStr"/>
-      <c r="N378" s="4" t="inlineStr"/>
+      <c r="N378" t="inlineStr"/>
+      <c r="O378" s="4" t="inlineStr"/>
     </row>
     <row r="379" ht="32" customHeight="1">
       <c r="A379" s="5" t="inlineStr">
@@ -24265,7 +24706,8 @@
         </is>
       </c>
       <c r="M379" s="6" t="inlineStr"/>
-      <c r="N379" s="6" t="inlineStr">
+      <c r="N379" t="inlineStr"/>
+      <c r="O379" s="6" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
@@ -24321,7 +24763,8 @@
         </is>
       </c>
       <c r="M380" s="4" t="inlineStr"/>
-      <c r="N380" s="4" t="inlineStr">
+      <c r="N380" t="inlineStr"/>
+      <c r="O380" s="4" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -24377,7 +24820,8 @@
         </is>
       </c>
       <c r="M381" s="6" t="inlineStr"/>
-      <c r="N381" s="6" t="inlineStr">
+      <c r="N381" t="inlineStr"/>
+      <c r="O381" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -24433,7 +24877,8 @@
         </is>
       </c>
       <c r="M382" s="4" t="inlineStr"/>
-      <c r="N382" s="4" t="inlineStr">
+      <c r="N382" t="inlineStr"/>
+      <c r="O382" s="4" t="inlineStr">
         <is>
           <t>5.2</t>
         </is>
@@ -24489,7 +24934,8 @@
         </is>
       </c>
       <c r="M383" s="6" t="inlineStr"/>
-      <c r="N383" s="6" t="inlineStr">
+      <c r="N383" t="inlineStr"/>
+      <c r="O383" s="6" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -24541,7 +24987,8 @@
       </c>
       <c r="L384" s="4" t="inlineStr"/>
       <c r="M384" s="4" t="inlineStr"/>
-      <c r="N384" s="4" t="inlineStr"/>
+      <c r="N384" t="inlineStr"/>
+      <c r="O384" s="4" t="inlineStr"/>
     </row>
     <row r="385" ht="32" customHeight="1">
       <c r="A385" s="5" t="inlineStr">
@@ -24589,7 +25036,8 @@
       </c>
       <c r="L385" s="6" t="inlineStr"/>
       <c r="M385" s="6" t="inlineStr"/>
-      <c r="N385" s="6" t="inlineStr"/>
+      <c r="N385" t="inlineStr"/>
+      <c r="O385" s="6" t="inlineStr"/>
     </row>
     <row r="386" ht="32" customHeight="1">
       <c r="A386" s="3" t="inlineStr">
@@ -24641,7 +25089,8 @@
         </is>
       </c>
       <c r="M386" s="4" t="inlineStr"/>
-      <c r="N386" s="4" t="inlineStr">
+      <c r="N386" t="inlineStr"/>
+      <c r="O386" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -24697,7 +25146,8 @@
         </is>
       </c>
       <c r="M387" s="6" t="inlineStr"/>
-      <c r="N387" s="6" t="inlineStr">
+      <c r="N387" t="inlineStr"/>
+      <c r="O387" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -24753,7 +25203,8 @@
         </is>
       </c>
       <c r="M388" s="4" t="inlineStr"/>
-      <c r="N388" s="4" t="inlineStr">
+      <c r="N388" t="inlineStr"/>
+      <c r="O388" s="4" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
@@ -24805,7 +25256,8 @@
       </c>
       <c r="L389" s="6" t="inlineStr"/>
       <c r="M389" s="6" t="inlineStr"/>
-      <c r="N389" s="6" t="inlineStr"/>
+      <c r="N389" t="inlineStr"/>
+      <c r="O389" s="6" t="inlineStr"/>
     </row>
     <row r="390" ht="32" customHeight="1">
       <c r="A390" s="3" t="inlineStr">
@@ -24857,7 +25309,8 @@
         </is>
       </c>
       <c r="M390" s="4" t="inlineStr"/>
-      <c r="N390" s="4" t="inlineStr">
+      <c r="N390" t="inlineStr"/>
+      <c r="O390" s="4" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
@@ -24913,7 +25366,8 @@
         </is>
       </c>
       <c r="M391" s="6" t="inlineStr"/>
-      <c r="N391" s="6" t="inlineStr">
+      <c r="N391" t="inlineStr"/>
+      <c r="O391" s="6" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -24969,7 +25423,8 @@
         </is>
       </c>
       <c r="M392" s="4" t="inlineStr"/>
-      <c r="N392" s="4" t="inlineStr">
+      <c r="N392" t="inlineStr"/>
+      <c r="O392" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -25021,7 +25476,8 @@
       </c>
       <c r="L393" s="6" t="inlineStr"/>
       <c r="M393" s="6" t="inlineStr"/>
-      <c r="N393" s="6" t="inlineStr"/>
+      <c r="N393" t="inlineStr"/>
+      <c r="O393" s="6" t="inlineStr"/>
     </row>
     <row r="394" ht="32" customHeight="1">
       <c r="A394" s="3" t="inlineStr">
@@ -25073,7 +25529,8 @@
         </is>
       </c>
       <c r="M394" s="4" t="inlineStr"/>
-      <c r="N394" s="4" t="inlineStr">
+      <c r="N394" t="inlineStr"/>
+      <c r="O394" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -25129,7 +25586,8 @@
         </is>
       </c>
       <c r="M395" s="6" t="inlineStr"/>
-      <c r="N395" s="6" t="inlineStr">
+      <c r="N395" t="inlineStr"/>
+      <c r="O395" s="6" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
@@ -25185,7 +25643,8 @@
         </is>
       </c>
       <c r="M396" s="4" t="inlineStr"/>
-      <c r="N396" s="4" t="inlineStr">
+      <c r="N396" t="inlineStr"/>
+      <c r="O396" s="4" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -25241,7 +25700,8 @@
         </is>
       </c>
       <c r="M397" s="6" t="inlineStr"/>
-      <c r="N397" s="6" t="inlineStr">
+      <c r="N397" t="inlineStr"/>
+      <c r="O397" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -25297,7 +25757,8 @@
         </is>
       </c>
       <c r="M398" s="4" t="inlineStr"/>
-      <c r="N398" s="4" t="inlineStr">
+      <c r="N398" t="inlineStr"/>
+      <c r="O398" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -25353,7 +25814,8 @@
         </is>
       </c>
       <c r="M399" s="6" t="inlineStr"/>
-      <c r="N399" s="6" t="inlineStr">
+      <c r="N399" t="inlineStr"/>
+      <c r="O399" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -25409,7 +25871,8 @@
         </is>
       </c>
       <c r="M400" s="4" t="inlineStr"/>
-      <c r="N400" s="4" t="inlineStr">
+      <c r="N400" t="inlineStr"/>
+      <c r="O400" s="4" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -25461,7 +25924,8 @@
       </c>
       <c r="L401" s="6" t="inlineStr"/>
       <c r="M401" s="6" t="inlineStr"/>
-      <c r="N401" s="6" t="inlineStr"/>
+      <c r="N401" t="inlineStr"/>
+      <c r="O401" s="6" t="inlineStr"/>
     </row>
     <row r="402" ht="32" customHeight="1">
       <c r="A402" s="3" t="inlineStr">
@@ -25509,7 +25973,8 @@
       </c>
       <c r="L402" s="4" t="inlineStr"/>
       <c r="M402" s="4" t="inlineStr"/>
-      <c r="N402" s="4" t="inlineStr"/>
+      <c r="N402" t="inlineStr"/>
+      <c r="O402" s="4" t="inlineStr"/>
     </row>
     <row r="403" ht="32" customHeight="1">
       <c r="A403" s="5" t="inlineStr">
@@ -25557,7 +26022,8 @@
       </c>
       <c r="L403" s="6" t="inlineStr"/>
       <c r="M403" s="6" t="inlineStr"/>
-      <c r="N403" s="6" t="inlineStr"/>
+      <c r="N403" t="inlineStr"/>
+      <c r="O403" s="6" t="inlineStr"/>
     </row>
     <row r="404" ht="32" customHeight="1">
       <c r="A404" s="3" t="inlineStr">
@@ -25605,7 +26071,8 @@
       </c>
       <c r="L404" s="4" t="inlineStr"/>
       <c r="M404" s="4" t="inlineStr"/>
-      <c r="N404" s="4" t="inlineStr"/>
+      <c r="N404" t="inlineStr"/>
+      <c r="O404" s="4" t="inlineStr"/>
     </row>
     <row r="405" ht="32" customHeight="1">
       <c r="A405" s="5" t="inlineStr">
@@ -25653,7 +26120,8 @@
       </c>
       <c r="L405" s="6" t="inlineStr"/>
       <c r="M405" s="6" t="inlineStr"/>
-      <c r="N405" s="6" t="inlineStr"/>
+      <c r="N405" t="inlineStr"/>
+      <c r="O405" s="6" t="inlineStr"/>
     </row>
     <row r="406" ht="32" customHeight="1">
       <c r="A406" s="3" t="inlineStr">
@@ -25701,7 +26169,8 @@
       </c>
       <c r="L406" s="4" t="inlineStr"/>
       <c r="M406" s="4" t="inlineStr"/>
-      <c r="N406" s="4" t="inlineStr"/>
+      <c r="N406" t="inlineStr"/>
+      <c r="O406" s="4" t="inlineStr"/>
     </row>
     <row r="407" ht="32" customHeight="1">
       <c r="A407" s="5" t="inlineStr">
@@ -25749,7 +26218,8 @@
       </c>
       <c r="L407" s="6" t="inlineStr"/>
       <c r="M407" s="6" t="inlineStr"/>
-      <c r="N407" s="6" t="inlineStr"/>
+      <c r="N407" t="inlineStr"/>
+      <c r="O407" s="6" t="inlineStr"/>
     </row>
     <row r="408" ht="32" customHeight="1">
       <c r="A408" s="3" t="inlineStr">
@@ -25797,7 +26267,8 @@
       </c>
       <c r="L408" s="4" t="inlineStr"/>
       <c r="M408" s="4" t="inlineStr"/>
-      <c r="N408" s="4" t="inlineStr"/>
+      <c r="N408" t="inlineStr"/>
+      <c r="O408" s="4" t="inlineStr"/>
     </row>
     <row r="409" ht="32" customHeight="1">
       <c r="A409" s="5" t="inlineStr">
@@ -25849,7 +26320,8 @@
         </is>
       </c>
       <c r="M409" s="6" t="inlineStr"/>
-      <c r="N409" s="6" t="inlineStr">
+      <c r="N409" t="inlineStr"/>
+      <c r="O409" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -25901,7 +26373,8 @@
       </c>
       <c r="L410" s="4" t="inlineStr"/>
       <c r="M410" s="4" t="inlineStr"/>
-      <c r="N410" s="4" t="inlineStr"/>
+      <c r="N410" t="inlineStr"/>
+      <c r="O410" s="4" t="inlineStr"/>
     </row>
     <row r="411" ht="32" customHeight="1">
       <c r="A411" s="5" t="inlineStr">
@@ -25949,7 +26422,8 @@
       </c>
       <c r="L411" s="6" t="inlineStr"/>
       <c r="M411" s="6" t="inlineStr"/>
-      <c r="N411" s="6" t="inlineStr"/>
+      <c r="N411" t="inlineStr"/>
+      <c r="O411" s="6" t="inlineStr"/>
     </row>
     <row r="412" ht="32" customHeight="1">
       <c r="A412" s="3" t="inlineStr">
@@ -26001,7 +26475,8 @@
         </is>
       </c>
       <c r="M412" s="4" t="inlineStr"/>
-      <c r="N412" s="4" t="inlineStr">
+      <c r="N412" t="inlineStr"/>
+      <c r="O412" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -26053,7 +26528,8 @@
       </c>
       <c r="L413" s="6" t="inlineStr"/>
       <c r="M413" s="6" t="inlineStr"/>
-      <c r="N413" s="6" t="inlineStr"/>
+      <c r="N413" t="inlineStr"/>
+      <c r="O413" s="6" t="inlineStr"/>
     </row>
     <row r="414" ht="32" customHeight="1">
       <c r="A414" s="3" t="inlineStr">
@@ -26101,7 +26577,8 @@
       </c>
       <c r="L414" s="4" t="inlineStr"/>
       <c r="M414" s="4" t="inlineStr"/>
-      <c r="N414" s="4" t="inlineStr"/>
+      <c r="N414" t="inlineStr"/>
+      <c r="O414" s="4" t="inlineStr"/>
     </row>
     <row r="415" ht="32" customHeight="1">
       <c r="A415" s="5" t="inlineStr">
@@ -26153,7 +26630,8 @@
         </is>
       </c>
       <c r="M415" s="6" t="inlineStr"/>
-      <c r="N415" s="6" t="inlineStr">
+      <c r="N415" t="inlineStr"/>
+      <c r="O415" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -26205,7 +26683,8 @@
       </c>
       <c r="L416" s="4" t="inlineStr"/>
       <c r="M416" s="4" t="inlineStr"/>
-      <c r="N416" s="4" t="inlineStr"/>
+      <c r="N416" t="inlineStr"/>
+      <c r="O416" s="4" t="inlineStr"/>
     </row>
     <row r="417" ht="32" customHeight="1">
       <c r="A417" s="5" t="inlineStr">
@@ -26253,7 +26732,8 @@
       </c>
       <c r="L417" s="6" t="inlineStr"/>
       <c r="M417" s="6" t="inlineStr"/>
-      <c r="N417" s="6" t="inlineStr"/>
+      <c r="N417" t="inlineStr"/>
+      <c r="O417" s="6" t="inlineStr"/>
     </row>
     <row r="418" ht="32" customHeight="1">
       <c r="A418" s="3" t="inlineStr">
@@ -26301,7 +26781,8 @@
       </c>
       <c r="L418" s="4" t="inlineStr"/>
       <c r="M418" s="4" t="inlineStr"/>
-      <c r="N418" s="4" t="inlineStr"/>
+      <c r="N418" t="inlineStr"/>
+      <c r="O418" s="4" t="inlineStr"/>
     </row>
     <row r="419" ht="32" customHeight="1">
       <c r="A419" s="5" t="inlineStr">
@@ -26349,7 +26830,8 @@
       </c>
       <c r="L419" s="6" t="inlineStr"/>
       <c r="M419" s="6" t="inlineStr"/>
-      <c r="N419" s="6" t="inlineStr"/>
+      <c r="N419" t="inlineStr"/>
+      <c r="O419" s="6" t="inlineStr"/>
     </row>
     <row r="420" ht="32" customHeight="1">
       <c r="A420" s="3" t="inlineStr">
@@ -26397,7 +26879,8 @@
       </c>
       <c r="L420" s="4" t="inlineStr"/>
       <c r="M420" s="4" t="inlineStr"/>
-      <c r="N420" s="4" t="inlineStr"/>
+      <c r="N420" t="inlineStr"/>
+      <c r="O420" s="4" t="inlineStr"/>
     </row>
     <row r="421" ht="32" customHeight="1">
       <c r="A421" s="5" t="inlineStr">
@@ -26449,7 +26932,8 @@
         </is>
       </c>
       <c r="M421" s="6" t="inlineStr"/>
-      <c r="N421" s="6" t="inlineStr">
+      <c r="N421" t="inlineStr"/>
+      <c r="O421" s="6" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -26505,7 +26989,8 @@
         </is>
       </c>
       <c r="M422" s="4" t="inlineStr"/>
-      <c r="N422" s="4" t="inlineStr">
+      <c r="N422" t="inlineStr"/>
+      <c r="O422" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -26557,7 +27042,8 @@
       </c>
       <c r="L423" s="6" t="inlineStr"/>
       <c r="M423" s="6" t="inlineStr"/>
-      <c r="N423" s="6" t="inlineStr"/>
+      <c r="N423" t="inlineStr"/>
+      <c r="O423" s="6" t="inlineStr"/>
     </row>
     <row r="424" ht="32" customHeight="1">
       <c r="A424" s="3" t="inlineStr">
@@ -26609,7 +27095,8 @@
         </is>
       </c>
       <c r="M424" s="4" t="inlineStr"/>
-      <c r="N424" s="4" t="inlineStr">
+      <c r="N424" t="inlineStr"/>
+      <c r="O424" s="4" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
@@ -26665,7 +27152,8 @@
         </is>
       </c>
       <c r="M425" s="6" t="inlineStr"/>
-      <c r="N425" s="6" t="inlineStr">
+      <c r="N425" t="inlineStr"/>
+      <c r="O425" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -26717,7 +27205,8 @@
       </c>
       <c r="L426" s="4" t="inlineStr"/>
       <c r="M426" s="4" t="inlineStr"/>
-      <c r="N426" s="4" t="inlineStr"/>
+      <c r="N426" t="inlineStr"/>
+      <c r="O426" s="4" t="inlineStr"/>
     </row>
     <row r="427" ht="32" customHeight="1">
       <c r="A427" s="5" t="inlineStr">
@@ -26765,7 +27254,8 @@
       </c>
       <c r="L427" s="6" t="inlineStr"/>
       <c r="M427" s="6" t="inlineStr"/>
-      <c r="N427" s="6" t="inlineStr"/>
+      <c r="N427" t="inlineStr"/>
+      <c r="O427" s="6" t="inlineStr"/>
     </row>
     <row r="428" ht="32" customHeight="1">
       <c r="A428" s="3" t="inlineStr">
@@ -26817,7 +27307,8 @@
         </is>
       </c>
       <c r="M428" s="4" t="inlineStr"/>
-      <c r="N428" s="4" t="inlineStr">
+      <c r="N428" t="inlineStr"/>
+      <c r="O428" s="4" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -26873,7 +27364,8 @@
         </is>
       </c>
       <c r="M429" s="6" t="inlineStr"/>
-      <c r="N429" s="6" t="inlineStr">
+      <c r="N429" t="inlineStr"/>
+      <c r="O429" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -26929,7 +27421,8 @@
         </is>
       </c>
       <c r="M430" s="4" t="inlineStr"/>
-      <c r="N430" s="4" t="inlineStr">
+      <c r="N430" t="inlineStr"/>
+      <c r="O430" s="4" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
@@ -26981,7 +27474,8 @@
       </c>
       <c r="L431" s="6" t="inlineStr"/>
       <c r="M431" s="6" t="inlineStr"/>
-      <c r="N431" s="6" t="inlineStr"/>
+      <c r="N431" t="inlineStr"/>
+      <c r="O431" s="6" t="inlineStr"/>
     </row>
     <row r="432" ht="32" customHeight="1">
       <c r="A432" s="3" t="inlineStr">
@@ -27033,7 +27527,8 @@
         </is>
       </c>
       <c r="M432" s="4" t="inlineStr"/>
-      <c r="N432" s="4" t="inlineStr">
+      <c r="N432" t="inlineStr"/>
+      <c r="O432" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -27085,7 +27580,8 @@
       </c>
       <c r="L433" s="6" t="inlineStr"/>
       <c r="M433" s="6" t="inlineStr"/>
-      <c r="N433" s="6" t="inlineStr"/>
+      <c r="N433" t="inlineStr"/>
+      <c r="O433" s="6" t="inlineStr"/>
     </row>
     <row r="434" ht="32" customHeight="1">
       <c r="A434" s="3" t="inlineStr">
@@ -27137,7 +27633,8 @@
         </is>
       </c>
       <c r="M434" s="4" t="inlineStr"/>
-      <c r="N434" s="4" t="inlineStr">
+      <c r="N434" t="inlineStr"/>
+      <c r="O434" s="4" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -27193,7 +27690,8 @@
         </is>
       </c>
       <c r="M435" s="6" t="inlineStr"/>
-      <c r="N435" s="6" t="inlineStr">
+      <c r="N435" t="inlineStr"/>
+      <c r="O435" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -27245,7 +27743,8 @@
       </c>
       <c r="L436" s="4" t="inlineStr"/>
       <c r="M436" s="4" t="inlineStr"/>
-      <c r="N436" s="4" t="inlineStr"/>
+      <c r="N436" t="inlineStr"/>
+      <c r="O436" s="4" t="inlineStr"/>
     </row>
     <row r="437" ht="32" customHeight="1">
       <c r="A437" s="5" t="inlineStr">
@@ -27293,7 +27792,8 @@
       </c>
       <c r="L437" s="6" t="inlineStr"/>
       <c r="M437" s="6" t="inlineStr"/>
-      <c r="N437" s="6" t="inlineStr"/>
+      <c r="N437" t="inlineStr"/>
+      <c r="O437" s="6" t="inlineStr"/>
     </row>
     <row r="438" ht="32" customHeight="1">
       <c r="A438" s="3" t="inlineStr">
@@ -27345,7 +27845,8 @@
         </is>
       </c>
       <c r="M438" s="4" t="inlineStr"/>
-      <c r="N438" s="4" t="inlineStr">
+      <c r="N438" t="inlineStr"/>
+      <c r="O438" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -27401,7 +27902,8 @@
         </is>
       </c>
       <c r="M439" s="6" t="inlineStr"/>
-      <c r="N439" s="6" t="inlineStr">
+      <c r="N439" t="inlineStr"/>
+      <c r="O439" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -27453,7 +27955,8 @@
       </c>
       <c r="L440" s="4" t="inlineStr"/>
       <c r="M440" s="4" t="inlineStr"/>
-      <c r="N440" s="4" t="inlineStr"/>
+      <c r="N440" t="inlineStr"/>
+      <c r="O440" s="4" t="inlineStr"/>
     </row>
     <row r="441" ht="32" customHeight="1">
       <c r="A441" s="5" t="inlineStr">
@@ -27501,7 +28004,8 @@
       </c>
       <c r="L441" s="6" t="inlineStr"/>
       <c r="M441" s="6" t="inlineStr"/>
-      <c r="N441" s="6" t="inlineStr"/>
+      <c r="N441" t="inlineStr"/>
+      <c r="O441" s="6" t="inlineStr"/>
     </row>
     <row r="442" ht="32" customHeight="1">
       <c r="A442" s="3" t="inlineStr">
@@ -27549,7 +28053,8 @@
       </c>
       <c r="L442" s="4" t="inlineStr"/>
       <c r="M442" s="4" t="inlineStr"/>
-      <c r="N442" s="4" t="inlineStr"/>
+      <c r="N442" t="inlineStr"/>
+      <c r="O442" s="4" t="inlineStr"/>
     </row>
     <row r="443" ht="32" customHeight="1">
       <c r="A443" s="5" t="inlineStr">
@@ -27597,7 +28102,8 @@
       </c>
       <c r="L443" s="6" t="inlineStr"/>
       <c r="M443" s="6" t="inlineStr"/>
-      <c r="N443" s="6" t="inlineStr"/>
+      <c r="N443" t="inlineStr"/>
+      <c r="O443" s="6" t="inlineStr"/>
     </row>
     <row r="444" ht="32" customHeight="1">
       <c r="A444" s="3" t="inlineStr">
@@ -27649,7 +28155,8 @@
         </is>
       </c>
       <c r="M444" s="4" t="inlineStr"/>
-      <c r="N444" s="4" t="inlineStr">
+      <c r="N444" t="inlineStr"/>
+      <c r="O444" s="4" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -27705,7 +28212,8 @@
         </is>
       </c>
       <c r="M445" s="6" t="inlineStr"/>
-      <c r="N445" s="6" t="inlineStr">
+      <c r="N445" t="inlineStr"/>
+      <c r="O445" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -27757,7 +28265,8 @@
       </c>
       <c r="L446" s="4" t="inlineStr"/>
       <c r="M446" s="4" t="inlineStr"/>
-      <c r="N446" s="4" t="inlineStr"/>
+      <c r="N446" t="inlineStr"/>
+      <c r="O446" s="4" t="inlineStr"/>
     </row>
     <row r="447" ht="32" customHeight="1">
       <c r="A447" s="5" t="inlineStr">
@@ -27809,7 +28318,8 @@
         </is>
       </c>
       <c r="M447" s="6" t="inlineStr"/>
-      <c r="N447" s="6" t="inlineStr">
+      <c r="N447" t="inlineStr"/>
+      <c r="O447" s="6" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -27861,7 +28371,8 @@
       </c>
       <c r="L448" s="4" t="inlineStr"/>
       <c r="M448" s="4" t="inlineStr"/>
-      <c r="N448" s="4" t="inlineStr"/>
+      <c r="N448" t="inlineStr"/>
+      <c r="O448" s="4" t="inlineStr"/>
     </row>
     <row r="449" ht="32" customHeight="1">
       <c r="A449" s="5" t="inlineStr">
@@ -27909,7 +28420,8 @@
       </c>
       <c r="L449" s="6" t="inlineStr"/>
       <c r="M449" s="6" t="inlineStr"/>
-      <c r="N449" s="6" t="inlineStr"/>
+      <c r="N449" t="inlineStr"/>
+      <c r="O449" s="6" t="inlineStr"/>
     </row>
     <row r="450" ht="32" customHeight="1">
       <c r="A450" s="3" t="inlineStr">
@@ -27961,7 +28473,8 @@
         </is>
       </c>
       <c r="M450" s="4" t="inlineStr"/>
-      <c r="N450" s="4" t="inlineStr">
+      <c r="N450" t="inlineStr"/>
+      <c r="O450" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -28013,7 +28526,8 @@
       </c>
       <c r="L451" s="6" t="inlineStr"/>
       <c r="M451" s="6" t="inlineStr"/>
-      <c r="N451" s="6" t="inlineStr"/>
+      <c r="N451" t="inlineStr"/>
+      <c r="O451" s="6" t="inlineStr"/>
     </row>
     <row r="452" ht="32" customHeight="1">
       <c r="A452" s="3" t="inlineStr">
@@ -28061,7 +28575,8 @@
       </c>
       <c r="L452" s="4" t="inlineStr"/>
       <c r="M452" s="4" t="inlineStr"/>
-      <c r="N452" s="4" t="inlineStr"/>
+      <c r="N452" t="inlineStr"/>
+      <c r="O452" s="4" t="inlineStr"/>
     </row>
     <row r="453" ht="32" customHeight="1">
       <c r="A453" s="5" t="inlineStr">
@@ -28113,7 +28628,8 @@
         </is>
       </c>
       <c r="M453" s="6" t="inlineStr"/>
-      <c r="N453" s="6" t="inlineStr">
+      <c r="N453" t="inlineStr"/>
+      <c r="O453" s="6" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
@@ -28165,7 +28681,8 @@
       </c>
       <c r="L454" s="4" t="inlineStr"/>
       <c r="M454" s="4" t="inlineStr"/>
-      <c r="N454" s="4" t="inlineStr"/>
+      <c r="N454" t="inlineStr"/>
+      <c r="O454" s="4" t="inlineStr"/>
     </row>
     <row r="455" ht="32" customHeight="1">
       <c r="A455" s="5" t="inlineStr">
@@ -28213,7 +28730,8 @@
       </c>
       <c r="L455" s="6" t="inlineStr"/>
       <c r="M455" s="6" t="inlineStr"/>
-      <c r="N455" s="6" t="inlineStr"/>
+      <c r="N455" t="inlineStr"/>
+      <c r="O455" s="6" t="inlineStr"/>
     </row>
     <row r="456" ht="32" customHeight="1">
       <c r="A456" s="3" t="inlineStr">
@@ -28265,7 +28783,8 @@
         </is>
       </c>
       <c r="M456" s="4" t="inlineStr"/>
-      <c r="N456" s="4" t="inlineStr">
+      <c r="N456" t="inlineStr"/>
+      <c r="O456" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -28321,7 +28840,8 @@
         </is>
       </c>
       <c r="M457" s="6" t="inlineStr"/>
-      <c r="N457" s="6" t="inlineStr">
+      <c r="N457" t="inlineStr"/>
+      <c r="O457" s="6" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -28373,7 +28893,8 @@
       </c>
       <c r="L458" s="4" t="inlineStr"/>
       <c r="M458" s="4" t="inlineStr"/>
-      <c r="N458" s="4" t="inlineStr"/>
+      <c r="N458" t="inlineStr"/>
+      <c r="O458" s="4" t="inlineStr"/>
     </row>
     <row r="459" ht="32" customHeight="1">
       <c r="A459" s="5" t="inlineStr">
@@ -28421,7 +28942,8 @@
       </c>
       <c r="L459" s="6" t="inlineStr"/>
       <c r="M459" s="6" t="inlineStr"/>
-      <c r="N459" s="6" t="inlineStr"/>
+      <c r="N459" t="inlineStr"/>
+      <c r="O459" s="6" t="inlineStr"/>
     </row>
     <row r="460" ht="32" customHeight="1">
       <c r="A460" s="3" t="inlineStr">
@@ -28469,7 +28991,8 @@
       </c>
       <c r="L460" s="4" t="inlineStr"/>
       <c r="M460" s="4" t="inlineStr"/>
-      <c r="N460" s="4" t="inlineStr"/>
+      <c r="N460" t="inlineStr"/>
+      <c r="O460" s="4" t="inlineStr"/>
     </row>
     <row r="461" ht="32" customHeight="1">
       <c r="A461" s="5" t="inlineStr">
@@ -28521,7 +29044,8 @@
         </is>
       </c>
       <c r="M461" s="6" t="inlineStr"/>
-      <c r="N461" s="6" t="inlineStr">
+      <c r="N461" t="inlineStr"/>
+      <c r="O461" s="6" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -28581,7 +29105,8 @@
         </is>
       </c>
       <c r="M462" s="4" t="inlineStr"/>
-      <c r="N462" s="4" t="inlineStr">
+      <c r="N462" t="inlineStr"/>
+      <c r="O462" s="4" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
